--- a/import/products.xlsx
+++ b/import/products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive - University of East Anglia\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E639A06-CEC2-4B25-9DB5-37DB29385EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9697FB21-355A-4BE3-8021-68032520CE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="345">
   <si>
     <t>Name</t>
   </si>
@@ -325,12 +325,804 @@
   <si>
     <t>micro-headend</t>
   </si>
+  <si>
+    <t>OM 10 0646</t>
+  </si>
+  <si>
+    <t>Increase your customer value by offering pay-TV content.
+Receive up to 6 DVB-S/S2 inputs and play out as 6 COFDM
+outputs.
+The OM 10 0646 comes with four CI slots for decryption
+of pay-TV over satellite. It is equipped with a USB interface,
+which makes it possible to create hotel info channels or
+advertisement videos. Pre-configured settings are available for
+a quick and easy set-up.
+WISI designs, manufactures and supports all products of the
+OM Micro Headend Series in-house. They can be wallmounted
+in two different positions without the need for a bulky rack.</t>
+  </si>
+  <si>
+    <t>WISI-OM-10-0646.png</t>
+  </si>
+  <si>
+    <t>WISI-OM-10-0646.pdf</t>
+  </si>
+  <si>
+    <t>Smart multiplexing before the CI slots enables a compact design</t>
+  </si>
+  <si>
+    <t>USB interface enables insertion of any video content</t>
+  </si>
+  <si>
+    <t>Impedance</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Input frequency range</t>
+  </si>
+  <si>
+    <t>Input frequency steps</t>
+  </si>
+  <si>
+    <t>Input level range</t>
+  </si>
+  <si>
+    <t>Modulation DVB-S</t>
+  </si>
+  <si>
+    <t>Symbol rate DVB-S</t>
+  </si>
+  <si>
+    <t>Modulation DVB-S2</t>
+  </si>
+  <si>
+    <t>Symbol rate DVB-S2</t>
+  </si>
+  <si>
+    <t>950 ... 2150 MHz</t>
+  </si>
+  <si>
+    <t>1 MHz</t>
+  </si>
+  <si>
+    <t>50 ... 90 dBuV</t>
+  </si>
+  <si>
+    <t>OPSK</t>
+  </si>
+  <si>
+    <t>1 ... 53 MSps</t>
+  </si>
+  <si>
+    <t>QPSK, 8PSK (EN 302 307),
+QPSK, 8PSK (EN 302 307), 16APSK, 32 APSK</t>
+  </si>
+  <si>
+    <t>1 ... 53 MSps (QPSK); 1 ... 45 MSps (8PSK); 1 ... 35 MSps (16APSK); 1 ... 28 MSps (32APSK)</t>
+  </si>
+  <si>
+    <t>OM Manager Android app available for smartphone and tablet access through bluetooth</t>
+  </si>
+  <si>
+    <t>Hotel mode eliminates the need for TV's to rescan transponders after input modifications</t>
+  </si>
+  <si>
+    <t>Receive, decrypt, convert and play-out using one headend to save space and costs</t>
+  </si>
+  <si>
+    <t>CI Processing</t>
+  </si>
+  <si>
+    <t>Number of PCMCIA slots</t>
+  </si>
+  <si>
+    <t>TS Processing</t>
+  </si>
+  <si>
+    <t>TS stuffing</t>
+  </si>
+  <si>
+    <t>SI-Table handling</t>
+  </si>
+  <si>
+    <t>NIT handling</t>
+  </si>
+  <si>
+    <t>PID remapping</t>
+  </si>
+  <si>
+    <t>COFDM Processing</t>
+  </si>
+  <si>
+    <t>Constellations</t>
+  </si>
+  <si>
+    <t>QPSK, 16-, 64-QAM</t>
+  </si>
+  <si>
+    <t>1/2,2/3,3/4,5/6,7/8</t>
+  </si>
+  <si>
+    <t>1/8, 1/16, 1/32</t>
+  </si>
+  <si>
+    <t>Guard Interval</t>
+  </si>
+  <si>
+    <t>FEC</t>
+  </si>
+  <si>
+    <t>FFT Mode</t>
+  </si>
+  <si>
+    <t>2k, 8k</t>
+  </si>
+  <si>
+    <t>&gt;40 dB</t>
+  </si>
+  <si>
+    <t>MER</t>
+  </si>
+  <si>
+    <t>Output frequency range</t>
+  </si>
+  <si>
+    <t>Output frequency steps</t>
+  </si>
+  <si>
+    <t>Number of Channels</t>
+  </si>
+  <si>
+    <t>Channel allocation</t>
+  </si>
+  <si>
+    <t>Return loss</t>
+  </si>
+  <si>
+    <t>adjacent (1 x 6)</t>
+  </si>
+  <si>
+    <t>6 pcs.</t>
+  </si>
+  <si>
+    <t>85 ... 100 dBuV</t>
+  </si>
+  <si>
+    <t>110 ... 862 MHz</t>
+  </si>
+  <si>
+    <t>75 Ω</t>
+  </si>
+  <si>
+    <t>≥14 dB (45 MHz), 1,5 dB/Octave but &gt;10 dB</t>
+  </si>
+  <si>
+    <t>Output attenuation</t>
+  </si>
+  <si>
+    <t>0 ... 15 dB (1 dB step)</t>
+  </si>
+  <si>
+    <t>F-socket</t>
+  </si>
+  <si>
+    <t>RJ45</t>
+  </si>
+  <si>
+    <t>USB</t>
+  </si>
+  <si>
+    <t>1 pcs.</t>
+  </si>
+  <si>
+    <t>5 pcs. (4x Input, 1x Output)</t>
+  </si>
+  <si>
+    <t>110 ... 240 V (50/60 Hz)</t>
+  </si>
+  <si>
+    <t>272 x 196 x 75 mm</t>
+  </si>
+  <si>
+    <t>Dimensions (width x height x depth)</t>
+  </si>
+  <si>
+    <t>Typ. &lt;40 W (Max. 50 W with 4 LNBs)</t>
+  </si>
+  <si>
+    <t>5 ... 45 °C</t>
+  </si>
+  <si>
+    <t>OM 10 0648</t>
+  </si>
+  <si>
+    <t>Increase your customer value by offering pay-TV content.
+Receive up to 6 DVB-S/S2 inputs and play out as 8 QAM/
+COFDM outputs.
+The OM 10 0648 comes with four CI slots for decryption
+of pay-TV over satellite. It is equipped with a USB interface,
+which makes it possible to create hotel info channels or
+advertisement videos. Pre-configured settings are available for
+a quick and easy set-up.
+WISI designs, manufactures and supports all products of the
+OM Micro Headend Series in-house. They can be wallmounted
+in two different positions without the need for a bulky rack.</t>
+  </si>
+  <si>
+    <t>WISI-OM-10-0648.png</t>
+  </si>
+  <si>
+    <t>WISI-OM-10-0648.pdf</t>
+  </si>
+  <si>
+    <t>Receive, decrypt, convert and play-out using one headend to save
+space and costs</t>
+  </si>
+  <si>
+    <t>QPSK</t>
+  </si>
+  <si>
+    <t>QPSK, 8PSK (EN 302 307), 16APSK, 32 APSK</t>
+  </si>
+  <si>
+    <t>1 ... 53 MSps (QPSK);
+1 ... 45 MSps (8PSK);
+1 ... 35 MSps (16APSK);
+1 ... 53 MSps (QPSK); 1 ... 45 MSps (8PSK); 1 ... 35 MSps (16APSK); 1 ... 28 MSps (32APSK)</t>
+  </si>
+  <si>
+    <t>QAM Processing</t>
+  </si>
+  <si>
+    <t>64-, 256- QAM</t>
+  </si>
+  <si>
+    <t>Symbol rate</t>
+  </si>
+  <si>
+    <t>4,45 ... 7,20 MSymb/s</t>
+  </si>
+  <si>
+    <t>1/2, 2/3, 3/4, 5/6, 7/8</t>
+  </si>
+  <si>
+    <t>110 ... 862 MHz (COFDM); 50 ... 862 MHz (QAM)</t>
+  </si>
+  <si>
+    <t>90 ... 105 dBuV</t>
+  </si>
+  <si>
+    <t>8 pcs</t>
+  </si>
+  <si>
+    <t>adjacent (2 blocks per 4 channels)</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>T-8800ZX</t>
+  </si>
+  <si>
+    <t>The operating carrier of IP network digital broadcast server software is the control center of the PA system. Installed in the main control room, it can effectively manage the entire broadcast system in real time.</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>ITC T-8800ZX.png</t>
+  </si>
+  <si>
+    <t>ITC T-8800ZX.pdf</t>
+  </si>
+  <si>
+    <t>It adopts high-strength aluminum alloy panel, metal shell, high-temperature paint, and has a simple and elegant appearance.</t>
+  </si>
+  <si>
+    <t>The dust-proof air duct design is adopted, which has low noise, high dust resistance, fast heat dissipation and stable operation of the whole machine.</t>
+  </si>
+  <si>
+    <t>Pure industrial design, excellent heat dissipation structure, strong anti-electromagnetic interference, AC100-240V wide voltage input.</t>
+  </si>
+  <si>
+    <t>It has a Zhaoxin KX-U6780A processor, which has multiple cores and threads and fast computing speed; it supports the domestic Kylin embedded operating system V10.</t>
+  </si>
+  <si>
+    <t>The server motherboard comes standard with 2 Gigabit network cards, 1 PS/2 interface, easy to manage and maintain, 6 COM interfaces, 8 USB interfaces, and a 2.1-channel independent sound card.</t>
+  </si>
+  <si>
+    <t>Pull-out keyboard and mouse design, VGA+DVI high-definition output interface, supports Blu-ray high-definition hardware decoding, and supports network or local 1080P video.</t>
+  </si>
+  <si>
+    <t>It has 1-channel short-circuit trigger startup interface, which is used for timing drive startup of external equipment to realize unattended function.</t>
+  </si>
+  <si>
+    <t>Supports recording storage function, and the recording file save path can be customized in the background.</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>17.3 inches</t>
+  </si>
+  <si>
+    <t>Resolution</t>
+  </si>
+  <si>
+    <t>1920(H)×1080(V)</t>
+  </si>
+  <si>
+    <t>300cd/m²</t>
+  </si>
+  <si>
+    <t>Brightness</t>
+  </si>
+  <si>
+    <t>80/80/85/85 (up/down/left/right)</t>
+  </si>
+  <si>
+    <t>Viewing angle</t>
+  </si>
+  <si>
+    <t>Ten-point capacitive touch screen</t>
+  </si>
+  <si>
+    <t>Touchscreen</t>
+  </si>
+  <si>
+    <t>CPU</t>
+  </si>
+  <si>
+    <t>T-8800K</t>
+  </si>
+  <si>
+    <t>T-8800RPW</t>
+  </si>
+  <si>
+    <t>T-8800RPA</t>
+  </si>
+  <si>
+    <t>Memory</t>
+  </si>
+  <si>
+    <t>Standard 1×8G DDR4 desktop memory</t>
+  </si>
+  <si>
+    <t>2.7GHz, 8 cores</t>
+  </si>
+  <si>
+    <t>2 × RJ45</t>
+  </si>
+  <si>
+    <t>Network port</t>
+  </si>
+  <si>
+    <t>Hard disk slot</t>
+  </si>
+  <si>
+    <t>I/O interface</t>
+  </si>
+  <si>
+    <t>Working temperature, humidity</t>
+  </si>
+  <si>
+    <t>Storage temperature and humidity</t>
+  </si>
+  <si>
+    <t>Power supply</t>
+  </si>
+  <si>
+    <t>Installation</t>
+  </si>
+  <si>
+    <t>Software operating platform</t>
+  </si>
+  <si>
+    <t>Net weight</t>
+  </si>
+  <si>
+    <t>Dimensions (L x W x H)</t>
+  </si>
+  <si>
+    <t>484×339.5×353.5mm</t>
+  </si>
+  <si>
+    <t>20kg</t>
+  </si>
+  <si>
+    <t>Supports deployment of Kylin desktop operating system (Zhaoxin version) V10</t>
+  </si>
+  <si>
+    <t>Rack-mount or desktop</t>
+  </si>
+  <si>
+    <t>AC100-240V 300W</t>
+  </si>
+  <si>
+    <t>-10℃-60℃, 5%～95% (non-condensing state)</t>
+  </si>
+  <si>
+    <t>0℃-50℃, 5%～95% (non-condensing state)</t>
+  </si>
+  <si>
+    <t>Standard 1×256G M.2 solid state drive, supports expansion of 1×2.5" or 1×3.5" hard drive</t>
+  </si>
+  <si>
+    <t>1×VGA, 1×DVI, 2×LAN, 1×IPMI, 6×COM RS232 (COM3/4 supports RS232/RS485), 4×USB2.0, 4xUSB3.0, 1×PS/2, 1×MIC IN, 1×LINE OUT, 1×LINE IN, 1×TRIGGER INPUT</t>
+  </si>
+  <si>
+    <t>The controller is the core equipment of the broadcasting system, which is mainly responsible for controlling, managing and scheduling the broadcasting content and equipment on campus. It is usually used in schools and other institutions to provide functions such as information release, emergency notification, safety alarm and daily broadcasting.</t>
+  </si>
+  <si>
+    <t>ITC T-8800K.png</t>
+  </si>
+  <si>
+    <t>ITC T-8800K.pdf</t>
+  </si>
+  <si>
+    <t>Industrial-grade 1U cabinet chassis has a stable structure and excellent anti-electromagnetic interference and anti-radiation capabilities.</t>
+  </si>
+  <si>
+    <t>The CPU adopts an octa-core 64-bit big and small core architecture, 4*Cortex-A76+4*Cortex-A55, main frequency : 2.4GHz.</t>
+  </si>
+  <si>
+    <t>Running memory LPDDR4: 8GB.</t>
+  </si>
+  <si>
+    <t>Built-in EMMC storage capacity 128GB + 256G solid state drive.</t>
+  </si>
+  <si>
+    <t>Supports mainstream audio formats such as MP3, WAV, FLAC, OGG, AAC, OPUS, etc.</t>
+  </si>
+  <si>
+    <t>Supports NPU 6TOPS computing power.</t>
+  </si>
+  <si>
+    <t>It has 1-channel HDMI output interface and 1-channel line OUT audio output interface.</t>
+  </si>
+  <si>
+    <t>It has dual Ethernet RJ45 interfaces and supports 10/100/1000M adaptive Ethernet connection.</t>
+  </si>
+  <si>
+    <t>It has 2 USB2.0 ports and 2 USB3.0 ports (1 3.0 port is used for OTG upgrade).</t>
+  </si>
+  <si>
+    <t>With a one-touch reset and restart button, users can restart the device system with one click.</t>
+  </si>
+  <si>
+    <t>Supports Linux operating system and is compatible with any network structure such as routers, switches, bridge gateways, Modems, Internet, 2G, 3G, 4G, multicast, unicast , etc.</t>
+  </si>
+  <si>
+    <t>Digital products are easy to expand, are not restricted by geographical location, do not require additional computer room management equipment, adopt the design concept of common network and line construction-free, and are easy to install.</t>
+  </si>
+  <si>
+    <t>The broadcast system supports remote firmware upgrades for terminals, eliminating the need to perform local upgrades on the terminals, thus reducing the workload of maintenance personnel.</t>
+  </si>
+  <si>
+    <t>RK3588 octa-core 64-bit big and small core architecture, 4*Cortex-A76 + 4*Cortex-A55, main frequency: 2.4GHz</t>
+  </si>
+  <si>
+    <t>GPU</t>
+  </si>
+  <si>
+    <t>Mali-G610 MC4 processing engine</t>
+  </si>
+  <si>
+    <t>Support 6TOPS computing power</t>
+  </si>
+  <si>
+    <t>LPDDR4:8GB</t>
+  </si>
+  <si>
+    <t>NPU</t>
+  </si>
+  <si>
+    <t>Built-in storage capacity</t>
+  </si>
+  <si>
+    <t>EMMC : 128GB+256GB solid state drive</t>
+  </si>
+  <si>
+    <t>With 1 HDMI interface</t>
+  </si>
+  <si>
+    <t>Display interface</t>
+  </si>
+  <si>
+    <t>USB interface</t>
+  </si>
+  <si>
+    <t>With dual Ethernet RJ45 interface, support 10/100/1000M adaptive Ethernet connection</t>
+  </si>
+  <si>
+    <t>With 2 USB2.0 ports, 2 USB3.0 ports (1 3.0 port is used for OTA upgrade)</t>
+  </si>
+  <si>
+    <t>Support IPV6 and IPV4 protocols</t>
+  </si>
+  <si>
+    <t>Support agreement</t>
+  </si>
+  <si>
+    <t>Audio format</t>
+  </si>
+  <si>
+    <t>≤ 0.1 %</t>
+  </si>
+  <si>
+    <t>LINE OUT output distortion</t>
+  </si>
+  <si>
+    <t>LINE OUT output signal-to-noise ratio</t>
+  </si>
+  <si>
+    <t>＞ 73 dB</t>
+  </si>
+  <si>
+    <t>800 mV</t>
+  </si>
+  <si>
+    <t>LINE OUT output amplitude</t>
+  </si>
+  <si>
+    <t>LINE OUT output impedance</t>
+  </si>
+  <si>
+    <t>470Ω</t>
+  </si>
+  <si>
+    <t>≤ 50W</t>
+  </si>
+  <si>
+    <t>≤ 5W</t>
+  </si>
+  <si>
+    <t>Standby power consumption</t>
+  </si>
+  <si>
+    <t>Operating temperature</t>
+  </si>
+  <si>
+    <t>Working environment humidity</t>
+  </si>
+  <si>
+    <t>Input power</t>
+  </si>
+  <si>
+    <t>Operating system</t>
+  </si>
+  <si>
+    <t>Linux</t>
+  </si>
+  <si>
+    <t>2.6kg</t>
+  </si>
+  <si>
+    <t>492.8 × 213 × 44 mm</t>
+  </si>
+  <si>
+    <t>～190-240V 50Hz</t>
+  </si>
+  <si>
+    <t>20% to 80% relative humidity, no condensation</t>
+  </si>
+  <si>
+    <t>-10℃ ～ 40℃</t>
+  </si>
+  <si>
+    <t>T-8800RP1 software</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>The broadcasting system management and control software is installed in the network broadcasting control center or computer. It is a comprehensive management platform for broadcasting system data exchange, system operation and functional operation. It integrates core technologies such as artificial intelligence, big data visualization, audio and video processing, electroacoustic design, and network technology to create a domestic broadcasting system with AI intelligence, Hi-Fi sound quality, low latency and high reliability.</t>
+  </si>
+  <si>
+    <t>ITC T-8800RP1 software.png</t>
+  </si>
+  <si>
+    <t>ITC T-8800RP1 software.pdf</t>
+  </si>
+  <si>
+    <t>Centralized Platform Management</t>
+  </si>
+  <si>
+    <t>Uniformly manages all audio terminals (voice consoles, intercom, broadcast, fire alarm) with real-time status monitoring (IP, online status, volume, tasks).</t>
+  </si>
+  <si>
+    <t>B/S architecture - manage everything via web browser: terminals, users, scheduling, audio files, and recordings.</t>
+  </si>
+  <si>
+    <t>Runs as a background system service with automatic startup for enterprise-level stability.</t>
+  </si>
+  <si>
+    <t>Audio &amp; Broadcast</t>
+  </si>
+  <si>
+    <t>Full-duplex voice and data exchange; supports one-click calling, intercom, help, and alarm modes.</t>
+  </si>
+  <si>
+    <t>Manages program libraries with scheduled playback and real-time on-demand media services.</t>
+  </si>
+  <si>
+    <t>Supports MP3, WAV, FLAC, OGG, AAC, OPUS formats; includes upload, transcoding, and sharing.</t>
+  </si>
+  <si>
+    <t>Anti-packet loss technology supports network packet loss rates above 37.5% for smooth audio.</t>
+  </si>
+  <si>
+    <t>User &amp; Management</t>
+  </si>
+  <si>
+    <t>Multiple login methods: password, PIN, and pattern; configurable lockout limits.</t>
+  </si>
+  <si>
+    <t>Multi-level, role-based permission management with per-terminal and per-group access control.</t>
+  </si>
+  <si>
+    <t>Supports creating/disabling users and one-click account management.</t>
+  </si>
+  <si>
+    <t>Flexible timed ringing with hourly, daily, weekly, monthly, and yearly modes; supports cloning and batch editing.</t>
+  </si>
+  <si>
+    <t>Scheduling &amp; Automation</t>
+  </si>
+  <si>
+    <t>Programmable timed tasks with multiple audio sources and execution testing.</t>
+  </si>
+  <si>
+    <t>Offline timed ringing works even when terminals are powered off.</t>
+  </si>
+  <si>
+    <t>Timed insertion mode auto-generates ringing tasks in bulk - no manual editing needed.</t>
+  </si>
+  <si>
+    <t>Electronic/online map with terminal deployment, real-time status viewing, GIS support, and one-click broadcasting.</t>
+  </si>
+  <si>
+    <t>Customizable terminal zone division for intuitive region-based management.</t>
+  </si>
+  <si>
+    <t>Map &amp; Zone Management</t>
+  </si>
+  <si>
+    <t>District/zone-wide fire alarm linkage with N±N modes, manual and digital triggers.</t>
+  </si>
+  <si>
+    <t>Anti-bullying keyword detection with TTS broadcast linkage and AI-powered early warning terminals.</t>
+  </si>
+  <si>
+    <t>Terminal tamper alarms with automatic deactivation support.</t>
+  </si>
+  <si>
+    <t>Safety &amp; Alarms</t>
+  </si>
+  <si>
+    <t>Remote firmware upgrades for all terminals — no local maintenance required.</t>
+  </si>
+  <si>
+    <t>System &amp; Maintenance</t>
+  </si>
+  <si>
+    <t>System detection: hard drive, memory, CPU, network, packet loss, audio similarity (DTW).</t>
+  </si>
+  <si>
+    <t>Full operation logging: every call, broadcast, and conversation is recorded.</t>
+  </si>
+  <si>
+    <t>SSL certificate support with one-click HTTPS activation.</t>
+  </si>
+  <si>
+    <t>Compatibility &amp; Deployment</t>
+  </si>
+  <si>
+    <t>Compatible with routers, switches, Internet, 3G/4G/5G networks, and IPv4/IPv6 dual-stack.</t>
+  </si>
+  <si>
+    <t>Supports Linux, Kylin, and UnionTech operating systems.</t>
+  </si>
+  <si>
+    <t>Multilingual support: Simplified/Traditional Chinese, English, Korean, Portuguese, Spanish, Russian, French, Arabic.</t>
+  </si>
+  <si>
+    <t>Background skinning, classic/simplified interface modes, and customizable homepage modules.</t>
+  </si>
+  <si>
+    <t>Built-in TTS with adjustable speech rate and voice package selection.</t>
+  </si>
+  <si>
+    <t>Drag-and-drop zero-code interface editor with 48 design styles and a component library.</t>
+  </si>
+  <si>
+    <t>UI &amp; Customization</t>
+  </si>
+  <si>
+    <t>IP digital broadcasting APP is an intelligent broadcasting software, which has music playback, terminal status and other functions in the playback system. It can meet various broadcasting application scenarios in schools, prisons, office buildings, exhibition centers, parks, scenic spots, stations, large commercial cities and other places.</t>
+  </si>
+  <si>
+    <t>T-8800PA software</t>
+  </si>
+  <si>
+    <t>ITC T-8800PA software.png</t>
+  </si>
+  <si>
+    <t>ITC T-8800PA software.pdf</t>
+  </si>
+  <si>
+    <t>The software supports the account and password provided by the login platform. Its functions include terminal status management, remote task management, session status management, broadcast room management (shouting broadcast/text broadcast), media library resource management and account information management modules.</t>
+  </si>
+  <si>
+    <t>Supports broadcasting function, including quick broadcasting, recording broadcasting, text broadcasting, media broadcasting, and collection broadcasting. The volume of the task can be controlled by the volume button on the phone:
+(1) It supports quick broadcast function to establish calls, which can be made to designated terminals or groups, and the volume can be adjusted in real time.
+(2) Supports voice push (recording), and can broadcast by sending a voice message.
+(3) Supports music broadcasting and can play the existing playlist music in the server.
+(4) Supports capture broadcast, and can collect the audio currently being played on the mobile phone for broadcasting.</t>
+  </si>
+  <si>
+    <t>Supports intercom function and supports 10 terminals for intercom.</t>
+  </si>
+  <si>
+    <t>Built-in TTS text-to-speech function, supports text-to-speech, can adjust 1-10 speech speed, number of loops, and select voice package (male/female).</t>
+  </si>
+  <si>
+    <t>Supports the initiation of text broadcasting tasks, as well as the use of text recognition or picture recognition for playback.</t>
+  </si>
+  <si>
+    <t>Supports viewing session status, including the status of ongoing tasks such as scheduled ringing, broadcast tasks, scheduled tasks, alarm tasks, ... and the number of ongoing tasks.</t>
+  </si>
+  <si>
+    <t>Supports viewing daily tasks, supports time filtering and selecting the task list of the corresponding date, supports viewing ongoing tasks, and supports viewing tasks in the form of a timeline.</t>
+  </si>
+  <si>
+    <t>Supports configuration of task priority, volume, playback mode, and mixing configuration.</t>
+  </si>
+  <si>
+    <t>Audiobook mode: supports automatic playback of broadcast audio content and switches to audiobook mode, which can automatically play according to the audiobook mode type.</t>
+  </si>
+  <si>
+    <t>Supports uploading built-in music in mobile phones: You can manually upload the built-in music files of Android phones to the server, and support on-demand playback after uploading.</t>
+  </si>
+  <si>
+    <t>It has a task manager function that can manage the current playback task, and can operate the previous/next song/pause or resume/task volume/end task/switch playback mode.</t>
+  </si>
+  <si>
+    <t>Supports viewing detailed information of all terminals online, offline, current tasks, ... supports searching terminals and viewing terminal lists.</t>
+  </si>
+  <si>
+    <t>Supports viewing the total number of device uses, total device usage time, number of tasks executed, and supports editing personal information, including avatar, account password, pattern password, and PIN code.</t>
+  </si>
+  <si>
+    <t>Supports switching between normal and night mode interface effects to protect eyesight.</t>
+  </si>
+  <si>
+    <t>Supports Chinese and English language switching.</t>
+  </si>
+  <si>
+    <t>It supports access to the broadcasting system through cloud services. The APP software broadcasts, manages information, queries terminal status, broadcasts, intercoms, plays music on demand, converts text to speech (TTS), and edits common phrases to system terminals through 4G/5G/WiFi networks.</t>
+  </si>
+  <si>
+    <t>After accessing the broadcast system through cloud services, you can scan the QR code of the WEB cloud platform to log in to the APP account.</t>
+  </si>
+  <si>
+    <t>The software supports running on Android phones with Android 12.0 or above, and can be downloaded from Huawei and Xiaomi app stores.</t>
+  </si>
+  <si>
+    <t>Recommended system configuration
+(1) Operating system: Android 12.0 and above
+(2) CPU: Snapdragon 888 chip
+(3) RAM: 12G
+(4) Storage: 256G</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,9 +1138,39 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13.2"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2328"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -371,7 +1193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -379,18 +1201,119 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="13">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -401,6 +1324,9 @@
           <color indexed="64"/>
         </top>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -416,7 +1342,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{485EF06A-B474-447D-A8F9-89BDB6093278}" name="Table1" displayName="Table1" ref="A1:G90" totalsRowShown="0" headerRowDxfId="2" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{485EF06A-B474-447D-A8F9-89BDB6093278}" name="Table1" displayName="Table1" ref="A1:G90" totalsRowShown="0" headerRowDxfId="12" tableBorderDxfId="11">
   <autoFilter ref="A1:G90" xr:uid="{485EF06A-B474-447D-A8F9-89BDB6093278}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{8B000398-16FD-4922-ADD1-EEFE78CEDB7B}" name="Name"/>
@@ -432,25 +1358,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D07E12D5-F913-47C1-AE7C-8E8ABA5B5C62}" name="Table3" displayName="Table3" ref="A1:E51" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:E51" xr:uid="{D07E12D5-F913-47C1-AE7C-8E8ABA5B5C62}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D07E12D5-F913-47C1-AE7C-8E8ABA5B5C62}" name="Table3" displayName="Table3" ref="A1:E196" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E196" xr:uid="{D07E12D5-F913-47C1-AE7C-8E8ABA5B5C62}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{EDC36D2A-2B52-4AA0-B51B-167F8B40CFF4}" name="ProductName"/>
-    <tableColumn id="2" xr3:uid="{138AD29A-C3D3-4F84-9FA0-3ED6F72D8DD1}" name="tabName"/>
-    <tableColumn id="3" xr3:uid="{71BE44F6-AC63-4D06-A509-C0526FF17ED7}" name="SectionName"/>
-    <tableColumn id="4" xr3:uid="{392314CC-381F-497D-8729-4EF92F415A5C}" name="Label"/>
-    <tableColumn id="5" xr3:uid="{B9158384-C102-4C9C-9CD1-040535A2405F}" name="Value"/>
+    <tableColumn id="1" xr3:uid="{EDC36D2A-2B52-4AA0-B51B-167F8B40CFF4}" name="ProductName" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{138AD29A-C3D3-4F84-9FA0-3ED6F72D8DD1}" name="tabName" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{71BE44F6-AC63-4D06-A509-C0526FF17ED7}" name="SectionName" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{392314CC-381F-497D-8729-4EF92F415A5C}" name="Label" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{B9158384-C102-4C9C-9CD1-040535A2405F}" name="Value" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2FA1D685-D8D8-4A34-AB8D-1A46F55D4A8E}" name="Table2" displayName="Table2" ref="A1:B41" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:B41" xr:uid="{2FA1D685-D8D8-4A34-AB8D-1A46F55D4A8E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2FA1D685-D8D8-4A34-AB8D-1A46F55D4A8E}" name="Table2" displayName="Table2" ref="A1:B42" totalsRowShown="0" headerRowDxfId="10" dataDxfId="7">
+  <autoFilter ref="A1:B42" xr:uid="{2FA1D685-D8D8-4A34-AB8D-1A46F55D4A8E}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B6913FB2-003F-4F8F-88B4-A069ABD8343E}" name="ProductName"/>
-    <tableColumn id="2" xr3:uid="{4F86F527-609B-41A7-8685-657266DE69B4}" name="Bullets"/>
+    <tableColumn id="1" xr3:uid="{B6913FB2-003F-4F8F-88B4-A069ABD8343E}" name="ProductName" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{4F86F527-609B-41A7-8685-657266DE69B4}" name="Bullets" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -773,7 +1699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20BB1523-B97F-467F-B1CE-C9963C8C7490}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" customWidth="1"/>
@@ -831,6 +1757,144 @@
         <v>20</v>
       </c>
     </row>
+    <row r="3" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="315" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>179</v>
+      </c>
+      <c r="G5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>279</v>
+      </c>
+      <c r="B7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D7" t="s">
+        <v>281</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>323</v>
+      </c>
+      <c r="B8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" t="s">
+        <v>280</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>324</v>
+      </c>
+      <c r="G8" t="s">
+        <v>325</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -841,14 +1905,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8ACB312-7589-4E92-972B-4AEFAD0C5968}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:R196"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
     <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" customWidth="1"/>
-    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="98" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -869,571 +1933,3045 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D22" t="s">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D23" t="s">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D24" t="s">
+      <c r="C24" s="3"/>
+      <c r="D24" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="3" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D25" t="s">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D26" t="s">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D27" t="s">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="3" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D28" t="s">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="3" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D29" t="s">
+      <c r="C29" s="3"/>
+      <c r="D29" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="3" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D30" t="s">
+      <c r="C30" s="3"/>
+      <c r="D30" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D31" t="s">
+      <c r="C31" s="3"/>
+      <c r="D31" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="3" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D32" t="s">
+      <c r="C32" s="3"/>
+      <c r="D32" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="3" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D33" t="s">
+      <c r="C33" s="3"/>
+      <c r="D33" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="3" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D34" t="s">
+      <c r="C34" s="3"/>
+      <c r="D34" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D35" t="s">
+      <c r="C35" s="3"/>
+      <c r="D35" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="3">
         <v>76113</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D36" t="s">
+      <c r="C36" s="3"/>
+      <c r="D36" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="3">
         <v>85176200</v>
       </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E78" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="R92" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="R94" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A106" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" s="3"/>
+      <c r="D106" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="E106" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A107" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C107" s="3"/>
+      <c r="D107" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="E107" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A108" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C108" s="3"/>
+      <c r="D108" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A109" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109" s="3"/>
+      <c r="D109" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A110" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="E110" s="11" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A111" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C111" s="3"/>
+      <c r="D111" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A112" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C112" s="3"/>
+      <c r="D112" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E112" s="11" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C113" s="3"/>
+      <c r="D113" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E113" s="11" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A114" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114" s="3"/>
+      <c r="D114" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A115" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C115" s="3"/>
+      <c r="D115" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="A117" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C117" s="3"/>
+      <c r="D117" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A118" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C118" s="3"/>
+      <c r="D118" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E118" s="11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A119" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C119" s="3"/>
+      <c r="D119" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E119" s="11" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A120" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C120" s="3"/>
+      <c r="D120" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E120" s="11" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A121" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C121" s="3"/>
+      <c r="D121" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="E121" s="11" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A122" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C122" s="3"/>
+      <c r="D122" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E122" s="11" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C123" s="3"/>
+      <c r="D123" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C126" s="3"/>
+      <c r="D126" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C127" s="3"/>
+      <c r="D127" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C128" s="3"/>
+      <c r="D128" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="E128" s="11" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C129" s="3"/>
+      <c r="D129" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C130" s="3"/>
+      <c r="D130" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C131" s="3"/>
+      <c r="D131" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="E131" s="11" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C132" s="3"/>
+      <c r="D132" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C133" s="3"/>
+      <c r="D133" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E133" s="12" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C134" s="3"/>
+      <c r="D134" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C135" s="3"/>
+      <c r="D135" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E135" s="12" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C136" s="3"/>
+      <c r="D136" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C137" s="3"/>
+      <c r="D137" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E137" s="12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C138" s="3"/>
+      <c r="D138" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E138" s="12" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C139" s="3"/>
+      <c r="D139" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C140" s="3"/>
+      <c r="D140" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C141" s="3"/>
+      <c r="D141" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C142" s="3"/>
+      <c r="D142" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C143" s="3"/>
+      <c r="D143" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C144" s="3"/>
+      <c r="D144" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C145" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="D145" s="3"/>
+      <c r="E145" s="17" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D146" s="3"/>
+      <c r="E146" s="17" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D147" s="3"/>
+      <c r="E147" s="18" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D148" s="3"/>
+      <c r="E148" s="17" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D149" s="3"/>
+      <c r="E149" s="18" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D150" s="3"/>
+      <c r="E150" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D151" s="3"/>
+      <c r="E151" s="18" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D152" s="3"/>
+      <c r="E152" s="17" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D153" s="3"/>
+      <c r="E153" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D154" s="3"/>
+      <c r="E154" s="18" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D155" s="3"/>
+      <c r="E155" s="18" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D156" s="3"/>
+      <c r="E156" s="18" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D157" s="3"/>
+      <c r="E157" s="18" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D158" s="3"/>
+      <c r="E158" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D159" s="3"/>
+      <c r="E159" s="18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D160" s="3"/>
+      <c r="E160" s="18" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D161" s="3"/>
+      <c r="E161" s="18" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D162" s="3"/>
+      <c r="E162" s="18" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D163" s="3"/>
+      <c r="E163" s="18" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D164" s="3"/>
+      <c r="E164" s="18" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D165" s="3"/>
+      <c r="E165" s="18" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D166" s="3"/>
+      <c r="E166" s="18" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D167" s="3"/>
+      <c r="E167" s="18" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D168" s="3"/>
+      <c r="E168" s="17" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D169" s="3"/>
+      <c r="E169" s="18" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="33" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D170" s="3"/>
+      <c r="E170" s="18" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D171" s="3"/>
+      <c r="E171" s="18" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D172" s="3"/>
+      <c r="E172" s="18" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D173" s="3"/>
+      <c r="E173" s="18" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C174" s="3"/>
+      <c r="D174" s="15"/>
+      <c r="E174" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="186" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C175" s="3"/>
+      <c r="D175" s="15"/>
+      <c r="E175" s="21" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C176" s="3"/>
+      <c r="D176" s="16"/>
+      <c r="E176" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C177" s="3"/>
+      <c r="D177" s="16"/>
+      <c r="E177" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C178" s="3"/>
+      <c r="D178" s="19"/>
+      <c r="E178" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C179" s="3"/>
+      <c r="D179" s="20"/>
+      <c r="E179" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C180" s="3"/>
+      <c r="D180" s="20"/>
+      <c r="E180" s="4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C181" s="3"/>
+      <c r="D181" s="20"/>
+      <c r="E181" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="11" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="11" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="11" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
+      <c r="E185" s="11" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
+      <c r="E186" s="11" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
+      <c r="E187" s="11" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C188" s="3"/>
+      <c r="D188" s="3"/>
+      <c r="E188" s="11" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3"/>
+      <c r="E189" s="11" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C190" s="3"/>
+      <c r="D190" s="3"/>
+      <c r="E190" s="11" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
+      <c r="E191" s="11" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="86.25" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
+      <c r="E192" s="22" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A193" s="3"/>
+      <c r="B193" s="3"/>
+      <c r="C193" s="3"/>
+      <c r="D193" s="3"/>
+      <c r="E193" s="22"/>
+    </row>
+    <row r="194" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A194" s="3"/>
+      <c r="B194" s="3"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
+      <c r="E194" s="22"/>
+    </row>
+    <row r="195" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A195" s="3"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3"/>
+      <c r="E195" s="22"/>
+    </row>
+    <row r="196" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A196" s="3"/>
+      <c r="B196" s="3"/>
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
+      <c r="E196" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F8B551A-BE85-4FE7-95EC-34C5D2DF628B}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
-    <col min="2" max="2" width="73.140625" customWidth="1"/>
+    <col min="2" max="2" width="161.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1444,69 +4982,329 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>19</v>
       </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>279</v>
+      </c>
+      <c r="B41" s="5"/>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B42" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1746,20 +5544,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1b00f46c-3b5f-4331-86e9-781a15a27617" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1b00f46c-3b5f-4331-86e9-781a15a27617" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1782,14 +5580,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C53BC2E-8A9E-4A85-93E8-958094667844}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8B90F5-EBD9-46C8-A4AD-41D7B713BE29}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -1804,4 +5594,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C53BC2E-8A9E-4A85-93E8-958094667844}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/import/products.xlsx
+++ b/import/products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive - University of East Anglia\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9697FB21-355A-4BE3-8021-68032520CE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{621BBA3C-99C5-41B5-9C67-5D31EC190AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -609,9 +609,6 @@
     <t>The operating carrier of IP network digital broadcast server software is the control center of the PA system. Installed in the main control room, it can effectively manage the entire broadcast system in real time.</t>
   </si>
   <si>
-    <t>Controller</t>
-  </si>
-  <si>
     <t>ITC T-8800ZX.png</t>
   </si>
   <si>
@@ -913,9 +910,6 @@
   </si>
   <si>
     <t>T-8800RP1 software</t>
-  </si>
-  <si>
-    <t>Software</t>
   </si>
   <si>
     <t>The broadcasting system management and control software is installed in the network broadcasting control center or computer. It is a comprehensive management platform for broadcasting system data exchange, system operation and functional operation. It integrates core technologies such as artificial intelligence, big data visualization, audio and video processing, electroacoustic design, and network technology to create a domestic broadcasting system with AI intelligence, Hi-Fi sound quality, low latency and high reliability.</t>
@@ -1116,6 +1110,12 @@
 (2) CPU: Snapdragon 888 chip
 (3) RAM: 12G
 (4) Storage: 256G</t>
+  </si>
+  <si>
+    <t>controller</t>
+  </si>
+  <si>
+    <t>software</t>
   </si>
 </sst>
 </file>
@@ -1811,7 +1811,7 @@
         <v>175</v>
       </c>
       <c r="C5" t="s">
-        <v>178</v>
+        <v>343</v>
       </c>
       <c r="D5" t="s">
         <v>177</v>
@@ -1820,79 +1820,79 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
+        <v>178</v>
+      </c>
+      <c r="G5" t="s">
         <v>179</v>
-      </c>
-      <c r="G5" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B6" t="s">
         <v>175</v>
       </c>
       <c r="C6" t="s">
-        <v>178</v>
+        <v>343</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G6" t="s">
         <v>227</v>
-      </c>
-      <c r="G6" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B7" t="s">
         <v>175</v>
       </c>
       <c r="C7" t="s">
-        <v>280</v>
+        <v>344</v>
       </c>
       <c r="D7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B8" t="s">
         <v>175</v>
       </c>
       <c r="C8" t="s">
-        <v>280</v>
+        <v>344</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -3441,7 +3441,7 @@
         <v>171</v>
       </c>
       <c r="R92" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
@@ -3478,7 +3478,7 @@
         <v>172</v>
       </c>
       <c r="R94" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
@@ -3669,10 +3669,10 @@
       </c>
       <c r="C106" s="3"/>
       <c r="D106" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E106" s="11" t="s">
         <v>189</v>
-      </c>
-      <c r="E106" s="11" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -3684,10 +3684,10 @@
       </c>
       <c r="C107" s="3"/>
       <c r="D107" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E107" s="11" t="s">
         <v>191</v>
-      </c>
-      <c r="E107" s="11" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
@@ -3699,10 +3699,10 @@
       </c>
       <c r="C108" s="3"/>
       <c r="D108" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -3714,10 +3714,10 @@
       </c>
       <c r="C109" s="3"/>
       <c r="D109" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
@@ -3729,10 +3729,10 @@
       </c>
       <c r="C110" s="3"/>
       <c r="D110" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -3744,10 +3744,10 @@
       </c>
       <c r="C111" s="3"/>
       <c r="D111" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -3759,10 +3759,10 @@
       </c>
       <c r="C112" s="3"/>
       <c r="D112" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E112" s="11" t="s">
         <v>203</v>
-      </c>
-      <c r="E112" s="11" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -3774,10 +3774,10 @@
       </c>
       <c r="C113" s="3"/>
       <c r="D113" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -3789,10 +3789,10 @@
       </c>
       <c r="C114" s="3"/>
       <c r="D114" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
@@ -3804,10 +3804,10 @@
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -3819,10 +3819,10 @@
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="34.5" x14ac:dyDescent="0.25">
@@ -3834,10 +3834,10 @@
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -3849,10 +3849,10 @@
       </c>
       <c r="C118" s="3"/>
       <c r="D118" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -3864,10 +3864,10 @@
       </c>
       <c r="C119" s="3"/>
       <c r="D119" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -3879,10 +3879,10 @@
       </c>
       <c r="C120" s="3"/>
       <c r="D120" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
@@ -3894,10 +3894,10 @@
       </c>
       <c r="C121" s="3"/>
       <c r="D121" s="12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -3909,225 +3909,225 @@
       </c>
       <c r="C122" s="3"/>
       <c r="D122" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E122" s="11" t="s">
         <v>216</v>
-      </c>
-      <c r="E122" s="11" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C123" s="3"/>
       <c r="D123" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C124" s="3"/>
       <c r="D124" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E124" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="E124" s="4" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C125" s="3"/>
       <c r="D125" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C126" s="3"/>
       <c r="D126" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C127" s="3"/>
       <c r="D127" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="E127" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C128" s="3"/>
       <c r="D128" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C129" s="3"/>
       <c r="D129" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C130" s="3"/>
       <c r="D130" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C131" s="3"/>
       <c r="D131" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C132" s="3"/>
       <c r="D132" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C133" s="3"/>
       <c r="D133" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C134" s="3"/>
       <c r="D134" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E134" s="8" t="s">
         <v>260</v>
-      </c>
-      <c r="E134" s="8" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C135" s="3"/>
       <c r="D135" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E135" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C136" s="3"/>
       <c r="D136" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="E136" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="E136" s="4" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>65</v>
@@ -4137,552 +4137,552 @@
         <v>67</v>
       </c>
       <c r="E137" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C138" s="3"/>
       <c r="D138" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E138" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C139" s="3"/>
       <c r="D139" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C140" s="3"/>
       <c r="D140" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C141" s="3"/>
       <c r="D141" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C142" s="3"/>
       <c r="D142" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C143" s="3"/>
       <c r="D143" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C144" s="3"/>
       <c r="D144" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="E144" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="E144" s="4" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D145" s="3"/>
       <c r="E145" s="17" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D146" s="3"/>
       <c r="E146" s="17" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D147" s="3"/>
       <c r="E147" s="18" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D148" s="3"/>
       <c r="E148" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D149" s="3"/>
       <c r="E149" s="18" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="18" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D151" s="3"/>
       <c r="E151" s="18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D152" s="3"/>
       <c r="E152" s="17" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D153" s="3"/>
       <c r="E153" s="18" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D154" s="3"/>
       <c r="E154" s="18" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D155" s="3"/>
       <c r="E155" s="18" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D156" s="3"/>
       <c r="E156" s="18" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D157" s="3"/>
       <c r="E157" s="18" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D158" s="3"/>
       <c r="E158" s="18" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D159" s="3"/>
       <c r="E159" s="18" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D160" s="3"/>
       <c r="E160" s="18" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D161" s="3"/>
       <c r="E161" s="18" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D162" s="3"/>
       <c r="E162" s="18" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D163" s="3"/>
       <c r="E163" s="18" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D164" s="3"/>
       <c r="E164" s="18" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D165" s="3"/>
       <c r="E165" s="18" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D166" s="3"/>
       <c r="E166" s="18" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D167" s="3"/>
       <c r="E167" s="18" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D168" s="3"/>
       <c r="E168" s="17" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D169" s="3"/>
       <c r="E169" s="18" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="33" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D170" s="3"/>
       <c r="E170" s="18" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D171" s="3"/>
       <c r="E171" s="18" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D172" s="3"/>
       <c r="E172" s="18" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="18" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>26</v>
@@ -4690,12 +4690,12 @@
       <c r="C174" s="3"/>
       <c r="D174" s="15"/>
       <c r="E174" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="186" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>26</v>
@@ -4703,12 +4703,12 @@
       <c r="C175" s="3"/>
       <c r="D175" s="15"/>
       <c r="E175" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>26</v>
@@ -4716,12 +4716,12 @@
       <c r="C176" s="3"/>
       <c r="D176" s="16"/>
       <c r="E176" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>26</v>
@@ -4729,12 +4729,12 @@
       <c r="C177" s="3"/>
       <c r="D177" s="16"/>
       <c r="E177" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>26</v>
@@ -4742,12 +4742,12 @@
       <c r="C178" s="3"/>
       <c r="D178" s="19"/>
       <c r="E178" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>26</v>
@@ -4755,12 +4755,12 @@
       <c r="C179" s="3"/>
       <c r="D179" s="20"/>
       <c r="E179" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>26</v>
@@ -4768,12 +4768,12 @@
       <c r="C180" s="3"/>
       <c r="D180" s="20"/>
       <c r="E180" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>26</v>
@@ -4781,12 +4781,12 @@
       <c r="C181" s="3"/>
       <c r="D181" s="20"/>
       <c r="E181" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>26</v>
@@ -4794,12 +4794,12 @@
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="11" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>26</v>
@@ -4807,12 +4807,12 @@
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="11" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>26</v>
@@ -4820,12 +4820,12 @@
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="11" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>26</v>
@@ -4833,12 +4833,12 @@
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>26</v>
@@ -4846,12 +4846,12 @@
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="11" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>26</v>
@@ -4859,12 +4859,12 @@
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="11" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>26</v>
@@ -4872,12 +4872,12 @@
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="11" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>26</v>
@@ -4885,12 +4885,12 @@
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="11" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>26</v>
@@ -4898,12 +4898,12 @@
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="11" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>26</v>
@@ -4911,12 +4911,12 @@
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="11" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="86.25" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>26</v>
@@ -4924,7 +4924,7 @@
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="22" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
@@ -5131,7 +5131,7 @@
         <v>176</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5139,7 +5139,7 @@
         <v>176</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5147,7 +5147,7 @@
         <v>176</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5155,7 +5155,7 @@
         <v>176</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
@@ -5163,7 +5163,7 @@
         <v>176</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5171,7 +5171,7 @@
         <v>176</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5179,7 +5179,7 @@
         <v>176</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5187,122 +5187,122 @@
         <v>176</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B41" s="5"/>
     </row>
     <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B42" s="5"/>
     </row>

--- a/import/products.xlsx
+++ b/import/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive - University of East Anglia\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD93628-FC67-4F4D-81C6-0E978E5A6ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F50B1E5-2162-4F4B-934E-391AAE55D901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
   </bookViews>
@@ -1941,9 +1941,6 @@
     <t>T-8800KEY</t>
   </si>
   <si>
-    <t>Encryptor</t>
-  </si>
-  <si>
     <t>ITC T-8800KEY.png</t>
   </si>
   <si>
@@ -2857,6 +2854,9 @@
   </si>
   <si>
     <t>1.9kg</t>
+  </si>
+  <si>
+    <t>encryptor</t>
   </si>
 </sst>
 </file>
@@ -3997,24 +3997,24 @@
         <v>175</v>
       </c>
       <c r="C21" t="s">
-        <v>618</v>
+        <v>923</v>
       </c>
       <c r="D21" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="s">
+        <v>618</v>
+      </c>
+      <c r="G21" t="s">
         <v>619</v>
-      </c>
-      <c r="G21" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="24.75">
       <c r="A22" s="12" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B22" t="s">
         <v>175</v>
@@ -4023,44 +4023,44 @@
         <v>343</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="s">
+        <v>623</v>
+      </c>
+      <c r="G22" t="s">
         <v>624</v>
-      </c>
-      <c r="G22" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="24.75">
       <c r="A23" s="12" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B23" t="s">
         <v>175</v>
       </c>
       <c r="C23" t="s">
+        <v>661</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>662</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>663</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="s">
+        <v>663</v>
+      </c>
+      <c r="G23" t="s">
         <v>664</v>
-      </c>
-      <c r="G23" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="24.75">
       <c r="A24" s="12" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B24" t="s">
         <v>175</v>
@@ -4069,21 +4069,21 @@
         <v>514</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="s">
+        <v>681</v>
+      </c>
+      <c r="G24" t="s">
         <v>682</v>
-      </c>
-      <c r="G24" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="24.75">
       <c r="A25" s="12" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B25" t="s">
         <v>175</v>
@@ -4092,21 +4092,21 @@
         <v>514</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="s">
+        <v>704</v>
+      </c>
+      <c r="G25" t="s">
         <v>705</v>
-      </c>
-      <c r="G25" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="24.75">
       <c r="A26" s="12" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B26" t="s">
         <v>175</v>
@@ -4115,136 +4115,136 @@
         <v>514</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="s">
+        <v>718</v>
+      </c>
+      <c r="G26" t="s">
         <v>719</v>
-      </c>
-      <c r="G26" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="24.75">
       <c r="A27" s="12" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B27" t="s">
         <v>175</v>
       </c>
       <c r="C27" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="s">
+        <v>721</v>
+      </c>
+      <c r="G27" t="s">
         <v>722</v>
-      </c>
-      <c r="G27" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="24.75">
       <c r="A28" s="12" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B28" t="s">
         <v>175</v>
       </c>
       <c r="C28" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="s">
+        <v>758</v>
+      </c>
+      <c r="G28" t="s">
         <v>759</v>
-      </c>
-      <c r="G28" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="24.75">
       <c r="A29" s="12" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B29" t="s">
         <v>175</v>
       </c>
       <c r="C29" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="s">
+        <v>797</v>
+      </c>
+      <c r="G29" t="s">
         <v>798</v>
-      </c>
-      <c r="G29" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="24.75">
       <c r="A30" s="12" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B30" t="s">
         <v>175</v>
       </c>
       <c r="C30" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="s">
+        <v>806</v>
+      </c>
+      <c r="G30" t="s">
         <v>807</v>
-      </c>
-      <c r="G30" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="24.75">
       <c r="A31" s="12" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B31" t="s">
         <v>175</v>
       </c>
       <c r="C31" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="s">
+        <v>812</v>
+      </c>
+      <c r="G31" t="s">
         <v>813</v>
-      </c>
-      <c r="G31" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="24.75">
       <c r="A32" s="12" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B32" t="s">
         <v>175</v>
@@ -4253,21 +4253,21 @@
         <v>514</v>
       </c>
       <c r="D32" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="s">
+        <v>820</v>
+      </c>
+      <c r="G32" t="s">
         <v>821</v>
-      </c>
-      <c r="G32" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="24.75">
       <c r="A33" s="12" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B33" t="s">
         <v>175</v>
@@ -4276,21 +4276,21 @@
         <v>514</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="s">
+        <v>837</v>
+      </c>
+      <c r="G33" t="s">
         <v>838</v>
-      </c>
-      <c r="G33" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="24.75">
       <c r="A34" s="12" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B34" t="s">
         <v>175</v>
@@ -4299,21 +4299,21 @@
         <v>514</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34" t="s">
+        <v>847</v>
+      </c>
+      <c r="G34" t="s">
         <v>848</v>
-      </c>
-      <c r="G34" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="24.75">
       <c r="A35" s="12" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B35" t="s">
         <v>175</v>
@@ -4322,21 +4322,21 @@
         <v>514</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35" t="s">
+        <v>865</v>
+      </c>
+      <c r="G35" t="s">
         <v>866</v>
-      </c>
-      <c r="G35" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="90">
       <c r="A36" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B36" t="s">
         <v>175</v>
@@ -4345,21 +4345,21 @@
         <v>580</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="s">
+        <v>875</v>
+      </c>
+      <c r="G36" t="s">
         <v>876</v>
-      </c>
-      <c r="G36" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B37" t="s">
         <v>175</v>
@@ -4368,21 +4368,21 @@
         <v>514</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="s">
+        <v>895</v>
+      </c>
+      <c r="G37" t="s">
         <v>896</v>
-      </c>
-      <c r="G37" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="24.75">
       <c r="A38" s="12" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B38" t="s">
         <v>175</v>
@@ -4391,16 +4391,16 @@
         <v>514</v>
       </c>
       <c r="D38" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="s">
+        <v>915</v>
+      </c>
+      <c r="G38" t="s">
         <v>916</v>
-      </c>
-      <c r="G38" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -6010,111 +6010,111 @@
     </row>
     <row r="187" spans="1:2" ht="45">
       <c r="A187" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B187" s="17" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B188" s="17" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="30">
       <c r="A189" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B189" s="17" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B190" s="17" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B191" s="17" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B192" s="17" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B193" s="17" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="194" spans="1:2" ht="30">
       <c r="A194" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B194" s="17" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B195" s="17" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B196" s="17" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B197" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B198" s="17" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B199" s="17" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" s="18" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B200" s="17" t="s">
         <v>496</v>
@@ -6122,47 +6122,47 @@
     </row>
     <row r="201" spans="1:2" ht="34.5">
       <c r="A201" s="17" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="202" spans="1:2" ht="34.5">
       <c r="A202" s="17" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B202" s="13" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" s="17" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B203" s="17" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="204" spans="1:2" ht="30">
       <c r="A204" s="17" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B204" s="17" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" s="17" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B205" s="17" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="206" spans="1:2" ht="17.25">
       <c r="A206" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B206" s="13" t="s">
         <v>518</v>
@@ -6170,23 +6170,23 @@
     </row>
     <row r="207" spans="1:2" ht="34.5">
       <c r="A207" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B207" s="13" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="208" spans="1:2" ht="30">
       <c r="A208" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B208" s="17" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B209" s="17" t="s">
         <v>450</v>
@@ -6194,23 +6194,23 @@
     </row>
     <row r="210" spans="1:2" ht="30">
       <c r="A210" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B210" s="17" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B211" s="17" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B212" s="17" t="s">
         <v>457</v>
@@ -6218,31 +6218,31 @@
     </row>
     <row r="213" spans="1:2" ht="30">
       <c r="A213" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B213" s="17" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B214" s="17" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="215" spans="1:2" ht="30">
       <c r="A215" s="17" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B215" s="17" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="216" spans="1:2" ht="17.25">
       <c r="A216" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B216" s="13" t="s">
         <v>518</v>
@@ -6250,15 +6250,15 @@
     </row>
     <row r="217" spans="1:2" ht="51.75">
       <c r="A217" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B217" s="13" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="218" spans="1:2" ht="30">
       <c r="A218" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B218" s="17" t="s">
         <v>550</v>
@@ -6266,15 +6266,15 @@
     </row>
     <row r="219" spans="1:2" ht="30">
       <c r="A219" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B219" s="17" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="220" spans="1:2" ht="30">
       <c r="A220" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B220" s="17" t="s">
         <v>520</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="221" spans="1:2">
       <c r="A221" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B221" s="17" t="s">
         <v>450</v>
@@ -6290,15 +6290,15 @@
     </row>
     <row r="222" spans="1:2">
       <c r="A222" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B222" s="17" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="223" spans="1:2" ht="30">
       <c r="A223" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B223" s="17" t="s">
         <v>491</v>
@@ -6306,15 +6306,15 @@
     </row>
     <row r="224" spans="1:2" ht="30">
       <c r="A224" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B224" s="17" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="60">
       <c r="A225" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B225" s="17" t="s">
         <v>493</v>
@@ -6322,15 +6322,15 @@
     </row>
     <row r="226" spans="1:2" ht="30">
       <c r="A226" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B226" s="17" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="30">
       <c r="A227" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B227" s="17" t="s">
         <v>494</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="228" spans="1:2">
       <c r="A228" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B228" s="17" t="s">
         <v>457</v>
@@ -6346,7 +6346,7 @@
     </row>
     <row r="229" spans="1:2" ht="30">
       <c r="A229" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B229" s="17" t="s">
         <v>495</v>
@@ -6354,7 +6354,7 @@
     </row>
     <row r="230" spans="1:2">
       <c r="A230" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B230" s="17" t="s">
         <v>496</v>
@@ -6362,7 +6362,7 @@
     </row>
     <row r="231" spans="1:2" ht="30">
       <c r="A231" s="17" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B231" s="17" t="s">
         <v>498</v>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="232" spans="1:2" ht="17.25">
       <c r="A232" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B232" s="13" t="s">
         <v>518</v>
@@ -6378,15 +6378,15 @@
     </row>
     <row r="233" spans="1:2" ht="51.75">
       <c r="A233" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B233" s="13" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="30">
       <c r="A234" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B234" s="17" t="s">
         <v>550</v>
@@ -6394,15 +6394,15 @@
     </row>
     <row r="235" spans="1:2" ht="30">
       <c r="A235" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B235" s="17" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B236" s="17" t="s">
         <v>450</v>
@@ -6410,15 +6410,15 @@
     </row>
     <row r="237" spans="1:2">
       <c r="A237" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B237" s="17" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="30">
       <c r="A238" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B238" s="17" t="s">
         <v>491</v>
@@ -6426,15 +6426,15 @@
     </row>
     <row r="239" spans="1:2" ht="30">
       <c r="A239" s="17" t="s">
+        <v>716</v>
+      </c>
+      <c r="B239" s="17" t="s">
         <v>717</v>
-      </c>
-      <c r="B239" s="17" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="60">
       <c r="A240" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B240" s="17" t="s">
         <v>493</v>
@@ -6442,15 +6442,15 @@
     </row>
     <row r="241" spans="1:2" ht="30">
       <c r="A241" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B241" s="17" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="242" spans="1:2" ht="30">
       <c r="A242" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B242" s="17" t="s">
         <v>494</v>
@@ -6458,7 +6458,7 @@
     </row>
     <row r="243" spans="1:2">
       <c r="A243" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B243" s="17" t="s">
         <v>457</v>
@@ -6466,7 +6466,7 @@
     </row>
     <row r="244" spans="1:2" ht="30">
       <c r="A244" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B244" s="17" t="s">
         <v>495</v>
@@ -6474,7 +6474,7 @@
     </row>
     <row r="245" spans="1:2">
       <c r="A245" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B245" s="17" t="s">
         <v>496</v>
@@ -6482,7 +6482,7 @@
     </row>
     <row r="246" spans="1:2" ht="30">
       <c r="A246" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B246" s="17" t="s">
         <v>497</v>
@@ -6490,7 +6490,7 @@
     </row>
     <row r="247" spans="1:2" ht="30">
       <c r="A247" s="17" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B247" s="17" t="s">
         <v>498</v>
@@ -6498,103 +6498,103 @@
     </row>
     <row r="248" spans="1:2" ht="34.5">
       <c r="A248" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B248" s="13" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="249" spans="1:2" ht="34.5">
       <c r="A249" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B249" s="13" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="250" spans="1:2" ht="30">
       <c r="A250" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B250" s="17" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="251" spans="1:2" ht="45">
       <c r="A251" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B251" s="17" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B252" s="17" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B253" s="17" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="254" spans="1:2" ht="30">
       <c r="A254" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B254" s="17" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="255" spans="1:2" ht="30">
       <c r="A255" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B255" s="17" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B256" s="17" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="257" spans="1:2" ht="30">
       <c r="A257" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B257" s="17" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="258" spans="1:2" ht="30">
       <c r="A258" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B258" s="17" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="259" spans="1:2" ht="30">
       <c r="A259" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B259" s="17" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="260" spans="1:2" ht="30">
       <c r="A260" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B260" s="17" t="s">
         <v>374</v>
@@ -6602,39 +6602,39 @@
     </row>
     <row r="261" spans="1:2" ht="30">
       <c r="A261" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B261" s="17" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B262" s="17" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B263" s="17" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="264" spans="1:2" ht="30">
       <c r="A264" s="17" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B264" s="17" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="265" spans="1:2" ht="34.5">
       <c r="A265" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B265" s="13" t="s">
         <v>584</v>
@@ -6642,71 +6642,71 @@
     </row>
     <row r="266" spans="1:2" ht="34.5">
       <c r="A266" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B266" s="13" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="267" spans="1:2" ht="30">
       <c r="A267" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B267" s="17" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B268" s="17" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="269" spans="1:2" ht="45">
       <c r="A269" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B269" s="17" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B270" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="271" spans="1:2" ht="30">
       <c r="A271" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B271" s="17" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B272" s="17" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B273" s="17" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="274" spans="1:2" ht="30">
       <c r="A274" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B274" s="17" t="s">
         <v>491</v>
@@ -6714,23 +6714,23 @@
     </row>
     <row r="275" spans="1:2" ht="30">
       <c r="A275" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B275" s="17" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="276" spans="1:2" ht="45">
       <c r="A276" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B276" s="17" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="277" spans="1:2" ht="60">
       <c r="A277" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B277" s="17" t="s">
         <v>493</v>
@@ -6738,31 +6738,31 @@
     </row>
     <row r="278" spans="1:2">
       <c r="A278" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B278" s="17" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="279" spans="1:2" ht="30">
       <c r="A279" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B279" s="17" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B280" s="17" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="281" spans="1:2" ht="30">
       <c r="A281" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B281" s="17" t="s">
         <v>494</v>
@@ -6770,7 +6770,7 @@
     </row>
     <row r="282" spans="1:2">
       <c r="A282" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B282" s="17" t="s">
         <v>457</v>
@@ -6778,23 +6778,23 @@
     </row>
     <row r="283" spans="1:2" ht="30">
       <c r="A283" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B283" s="17" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B284" s="17" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B285" s="17" t="s">
         <v>496</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="286" spans="1:2" ht="30">
       <c r="A286" s="17" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B286" s="17" t="s">
         <v>498</v>
@@ -6810,7 +6810,7 @@
     </row>
     <row r="287" spans="1:2" ht="34.5">
       <c r="A287" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B287" s="13" t="s">
         <v>584</v>
@@ -6818,71 +6818,71 @@
     </row>
     <row r="288" spans="1:2" ht="34.5">
       <c r="A288" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B288" s="13" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="289" spans="1:2" ht="30">
       <c r="A289" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B289" s="17" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B290" s="17" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="291" spans="1:2" ht="45">
       <c r="A291" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B291" s="17" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B292" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="293" spans="1:2" ht="30">
       <c r="A293" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B293" s="17" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B294" s="17" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B295" s="17" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="296" spans="1:2" ht="30">
       <c r="A296" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B296" s="17" t="s">
         <v>491</v>
@@ -6890,23 +6890,23 @@
     </row>
     <row r="297" spans="1:2" ht="30">
       <c r="A297" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B297" s="17" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="298" spans="1:2" ht="45">
       <c r="A298" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B298" s="17" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="299" spans="1:2" ht="60">
       <c r="A299" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B299" s="17" t="s">
         <v>493</v>
@@ -6914,31 +6914,31 @@
     </row>
     <row r="300" spans="1:2" ht="30">
       <c r="A300" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B300" s="17" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="301" spans="1:2" ht="30">
       <c r="A301" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B301" s="17" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="302" spans="1:2">
       <c r="A302" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B302" s="17" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="303" spans="1:2" ht="30">
       <c r="A303" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B303" s="17" t="s">
         <v>494</v>
@@ -6946,7 +6946,7 @@
     </row>
     <row r="304" spans="1:2">
       <c r="A304" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B304" s="17" t="s">
         <v>457</v>
@@ -6954,23 +6954,23 @@
     </row>
     <row r="305" spans="1:2" ht="30">
       <c r="A305" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B305" s="17" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B306" s="17" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="307" spans="1:2">
       <c r="A307" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B307" s="17" t="s">
         <v>496</v>
@@ -6978,7 +6978,7 @@
     </row>
     <row r="308" spans="1:2" ht="30">
       <c r="A308" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B308" s="17" t="s">
         <v>498</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="309" spans="1:2" ht="34.5">
       <c r="A309" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B309" s="13" t="s">
         <v>584</v>
@@ -6994,71 +6994,71 @@
     </row>
     <row r="310" spans="1:2" ht="30">
       <c r="A310" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B310" s="17" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="311" spans="1:2" ht="30">
       <c r="A311" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B311" s="17" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B312" s="17" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="313" spans="1:2" ht="45">
       <c r="A313" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B313" s="17" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="314" spans="1:2">
       <c r="A314" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B314" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="315" spans="1:2" ht="30">
       <c r="A315" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B315" s="17" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B316" s="17" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B317" s="17" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="318" spans="1:2" ht="30">
       <c r="A318" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B318" s="17" t="s">
         <v>491</v>
@@ -7066,23 +7066,23 @@
     </row>
     <row r="319" spans="1:2" ht="30">
       <c r="A319" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B319" s="17" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="320" spans="1:2" ht="45">
       <c r="A320" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B320" s="17" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="321" spans="1:2" ht="60">
       <c r="A321" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B321" s="17" t="s">
         <v>493</v>
@@ -7090,31 +7090,31 @@
     </row>
     <row r="322" spans="1:2">
       <c r="A322" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B322" s="17" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="323" spans="1:2" ht="30">
       <c r="A323" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B323" s="17" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B324" s="17" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="325" spans="1:2" ht="30">
       <c r="A325" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B325" s="17" t="s">
         <v>494</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="326" spans="1:2">
       <c r="A326" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B326" s="17" t="s">
         <v>457</v>
@@ -7130,23 +7130,23 @@
     </row>
     <row r="327" spans="1:2" ht="30">
       <c r="A327" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B327" s="17" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B328" s="17" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B329" s="17" t="s">
         <v>496</v>
@@ -7154,7 +7154,7 @@
     </row>
     <row r="330" spans="1:2" ht="30">
       <c r="A330" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B330" s="17" t="s">
         <v>498</v>
@@ -7162,7 +7162,7 @@
     </row>
     <row r="331" spans="1:2" ht="34.5">
       <c r="A331" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B331" s="13" t="s">
         <v>584</v>
@@ -7170,71 +7170,71 @@
     </row>
     <row r="332" spans="1:2" ht="34.5">
       <c r="A332" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B332" s="13" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="333" spans="1:2" ht="30">
       <c r="A333" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B333" s="17" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B334" s="17" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="335" spans="1:2" ht="45">
       <c r="A335" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B335" s="17" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B336" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="337" spans="1:2" ht="30">
       <c r="A337" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B337" s="17" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B338" s="17" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="A339" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B339" s="17" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="340" spans="1:2" ht="30">
       <c r="A340" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B340" s="17" t="s">
         <v>491</v>
@@ -7242,23 +7242,23 @@
     </row>
     <row r="341" spans="1:2" ht="30">
       <c r="A341" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B341" s="17" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="342" spans="1:2" ht="45">
       <c r="A342" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B342" s="17" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="343" spans="1:2" ht="60">
       <c r="A343" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B343" s="17" t="s">
         <v>493</v>
@@ -7266,31 +7266,31 @@
     </row>
     <row r="344" spans="1:2" ht="30">
       <c r="A344" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B344" s="17" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="345" spans="1:2" ht="30">
       <c r="A345" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B345" s="17" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B346" s="17" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="347" spans="1:2" ht="30">
       <c r="A347" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B347" s="17" t="s">
         <v>494</v>
@@ -7298,7 +7298,7 @@
     </row>
     <row r="348" spans="1:2">
       <c r="A348" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B348" s="17" t="s">
         <v>457</v>
@@ -7306,23 +7306,23 @@
     </row>
     <row r="349" spans="1:2" ht="30">
       <c r="A349" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B349" s="17" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B350" s="17" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B351" s="17" t="s">
         <v>496</v>
@@ -7330,7 +7330,7 @@
     </row>
     <row r="352" spans="1:2" ht="30">
       <c r="A352" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B352" s="17" t="s">
         <v>498</v>
@@ -7338,39 +7338,39 @@
     </row>
     <row r="353" spans="1:2" ht="34.5">
       <c r="A353" s="17" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B353" s="13" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="354" spans="1:2" ht="51.75">
       <c r="A354" s="17" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B354" s="13" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="355" spans="1:2" ht="30">
       <c r="A355" s="17" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B355" s="17" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" s="17" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B356" s="17" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" s="17" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B357" s="17" t="s">
         <v>457</v>
@@ -7378,7 +7378,7 @@
     </row>
     <row r="358" spans="1:2">
       <c r="A358" s="17" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B358" s="17" t="s">
         <v>496</v>
@@ -7386,15 +7386,15 @@
     </row>
     <row r="359" spans="1:2">
       <c r="A359" s="17" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B359" s="17" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="360" spans="1:2" ht="30">
       <c r="A360" s="17" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B360" s="17" t="s">
         <v>498</v>
@@ -7402,39 +7402,39 @@
     </row>
     <row r="361" spans="1:2" ht="34.5">
       <c r="A361" s="17" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B361" s="13" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="362" spans="1:2" ht="51.75">
       <c r="A362" s="17" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B362" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="363" spans="1:2" ht="30">
       <c r="A363" s="17" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B363" s="17" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" s="17" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B364" s="17" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="365" spans="1:2">
       <c r="A365" s="17" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B365" s="17" t="s">
         <v>457</v>
@@ -7442,7 +7442,7 @@
     </row>
     <row r="366" spans="1:2">
       <c r="A366" s="17" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B366" s="17" t="s">
         <v>496</v>
@@ -7450,15 +7450,15 @@
     </row>
     <row r="367" spans="1:2">
       <c r="A367" s="17" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B367" s="17" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="368" spans="1:2" ht="30">
       <c r="A368" s="17" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B368" s="17" t="s">
         <v>498</v>
@@ -7466,55 +7466,55 @@
     </row>
     <row r="369" spans="1:2" ht="51.75">
       <c r="A369" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B369" s="13" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="370" spans="1:2">
       <c r="A370" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B370" s="17" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B371" s="17" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="372" spans="1:2" ht="45">
       <c r="A372" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B372" s="17" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="373" spans="1:2" ht="30">
       <c r="A373" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B373" s="17" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B374" s="17" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="375" spans="1:2">
       <c r="A375" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B375" s="17" t="s">
         <v>457</v>
@@ -7522,7 +7522,7 @@
     </row>
     <row r="376" spans="1:2" ht="30">
       <c r="A376" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B376" s="17" t="s">
         <v>524</v>
@@ -7530,7 +7530,7 @@
     </row>
     <row r="377" spans="1:2">
       <c r="A377" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B377" s="17" t="s">
         <v>496</v>
@@ -7538,15 +7538,15 @@
     </row>
     <row r="378" spans="1:2">
       <c r="A378" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B378" s="17" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="379" spans="1:2" ht="30">
       <c r="A379" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B379" s="17" t="s">
         <v>498</v>
@@ -7554,55 +7554,55 @@
     </row>
     <row r="380" spans="1:2" ht="51.75">
       <c r="A380" s="17" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B380" s="13" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="381" spans="1:2" ht="34.5">
       <c r="A381" s="17" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B381" s="13" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" s="17" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B382" s="17" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="383" spans="1:2" ht="45">
       <c r="A383" s="17" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B383" s="17" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="384" spans="1:2" ht="30">
       <c r="A384" s="17" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B384" s="17" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" s="17" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B385" s="17" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" s="17" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B386" s="17" t="s">
         <v>457</v>
@@ -7610,7 +7610,7 @@
     </row>
     <row r="387" spans="1:2" ht="30">
       <c r="A387" s="17" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B387" s="17" t="s">
         <v>524</v>
@@ -7618,7 +7618,7 @@
     </row>
     <row r="388" spans="1:2">
       <c r="A388" s="17" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B388" s="17" t="s">
         <v>496</v>
@@ -7626,15 +7626,15 @@
     </row>
     <row r="389" spans="1:2">
       <c r="A389" s="17" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B389" s="17" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="390" spans="1:2" ht="30">
       <c r="A390" s="17" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B390" s="17" t="s">
         <v>498</v>
@@ -7642,79 +7642,79 @@
     </row>
     <row r="391" spans="1:2" ht="17.25">
       <c r="A391" s="17" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B391" s="13" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="392" spans="1:2" ht="34.5">
       <c r="A392" s="17" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B392" s="13" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="393" spans="1:2">
       <c r="A393" s="17" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B393" s="17" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" s="17" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B394" s="17" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" s="17" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B395" s="17" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" s="17" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B396" s="17" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" s="17" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B397" s="17" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="398" spans="1:2" ht="34.5">
       <c r="A398" s="15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B398" s="13" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="399" spans="1:2" ht="34.5">
       <c r="A399" s="15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B399" s="13" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="400" spans="1:2" ht="34.5">
       <c r="A400" s="15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B400" s="13" t="s">
         <v>520</v>
@@ -7722,23 +7722,23 @@
     </row>
     <row r="401" spans="1:2">
       <c r="A401" s="15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B401" s="17" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="402" spans="1:2" ht="30">
       <c r="A402" s="15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B402" s="17" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="403" spans="1:2" ht="30">
       <c r="A403" s="15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B403" s="17" t="s">
         <v>494</v>
@@ -7746,7 +7746,7 @@
     </row>
     <row r="404" spans="1:2">
       <c r="A404" s="15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B404" s="17" t="s">
         <v>457</v>
@@ -7754,7 +7754,7 @@
     </row>
     <row r="405" spans="1:2" ht="30">
       <c r="A405" s="15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B405" s="17" t="s">
         <v>524</v>
@@ -7762,7 +7762,7 @@
     </row>
     <row r="406" spans="1:2">
       <c r="A406" s="15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B406" s="17" t="s">
         <v>523</v>
@@ -7770,31 +7770,31 @@
     </row>
     <row r="407" spans="1:2" ht="30">
       <c r="A407" s="15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B407" s="17" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="408" spans="1:2">
       <c r="A408" s="15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B408" s="17" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="409" spans="1:2" ht="34.5">
       <c r="A409" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B409" s="13" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="410" spans="1:2" ht="51.75">
       <c r="A410" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B410" s="13" t="s">
         <v>550</v>
@@ -7802,7 +7802,7 @@
     </row>
     <row r="411" spans="1:2" ht="34.5">
       <c r="A411" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B411" s="13" t="s">
         <v>519</v>
@@ -7810,7 +7810,7 @@
     </row>
     <row r="412" spans="1:2" ht="30">
       <c r="A412" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B412" s="17" t="s">
         <v>520</v>
@@ -7818,23 +7818,23 @@
     </row>
     <row r="413" spans="1:2">
       <c r="A413" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B413" s="17" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="414" spans="1:2" ht="30">
       <c r="A414" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B414" s="17" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="415" spans="1:2" ht="60">
       <c r="A415" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B415" s="17" t="s">
         <v>493</v>
@@ -7842,7 +7842,7 @@
     </row>
     <row r="416" spans="1:2" ht="30">
       <c r="A416" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B416" s="17" t="s">
         <v>551</v>
@@ -7850,7 +7850,7 @@
     </row>
     <row r="417" spans="1:2" ht="30">
       <c r="A417" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B417" s="17" t="s">
         <v>494</v>
@@ -7858,7 +7858,7 @@
     </row>
     <row r="418" spans="1:2">
       <c r="A418" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B418" s="17" t="s">
         <v>457</v>
@@ -7866,23 +7866,23 @@
     </row>
     <row r="419" spans="1:2" ht="30">
       <c r="A419" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B419" s="17" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B420" s="17" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B421" s="17" t="s">
         <v>523</v>
@@ -7890,18 +7890,18 @@
     </row>
     <row r="422" spans="1:2" ht="30">
       <c r="A422" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B422" s="17" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="423" spans="1:2">
       <c r="A423" s="15" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B423" s="17" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
   </sheetData>
@@ -14586,7 +14586,7 @@
     </row>
     <row r="439" spans="1:5">
       <c r="A439" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>596</v>
@@ -14601,7 +14601,7 @@
     </row>
     <row r="440" spans="1:5">
       <c r="A440" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>596</v>
@@ -14616,7 +14616,7 @@
     </row>
     <row r="441" spans="1:5">
       <c r="A441" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>596</v>
@@ -14626,12 +14626,12 @@
         <v>390</v>
       </c>
       <c r="E441" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="442" spans="1:5">
       <c r="A442" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>596</v>
@@ -14641,12 +14641,12 @@
         <v>527</v>
       </c>
       <c r="E442" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="443" spans="1:5">
       <c r="A443" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>596</v>
@@ -14656,72 +14656,72 @@
         <v>391</v>
       </c>
       <c r="E443" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="444" spans="1:5">
       <c r="A444" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C444" s="3"/>
       <c r="D444" t="s">
+        <v>641</v>
+      </c>
+      <c r="E444" t="s">
         <v>642</v>
-      </c>
-      <c r="E444" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="445" spans="1:5">
       <c r="A445" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C445" s="3"/>
       <c r="D445" t="s">
+        <v>643</v>
+      </c>
+      <c r="E445" t="s">
         <v>644</v>
-      </c>
-      <c r="E445" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="446" spans="1:5">
       <c r="A446" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C446" s="3"/>
       <c r="D446" t="s">
+        <v>645</v>
+      </c>
+      <c r="E446" t="s">
         <v>646</v>
-      </c>
-      <c r="E446" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="447" spans="1:5">
       <c r="A447" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C447" s="3"/>
       <c r="D447" t="s">
+        <v>647</v>
+      </c>
+      <c r="E447" t="s">
         <v>648</v>
-      </c>
-      <c r="E447" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="448" spans="1:5">
       <c r="A448" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>596</v>
@@ -14731,12 +14731,12 @@
         <v>406</v>
       </c>
       <c r="E448" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="449" spans="1:5">
       <c r="A449" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>596</v>
@@ -14746,12 +14746,12 @@
         <v>531</v>
       </c>
       <c r="E449" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="450" spans="1:5">
       <c r="A450" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>596</v>
@@ -14761,27 +14761,27 @@
         <v>530</v>
       </c>
       <c r="E450" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="451" spans="1:5">
       <c r="A451" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C451" s="3"/>
       <c r="D451" t="s">
+        <v>652</v>
+      </c>
+      <c r="E451" t="s">
         <v>653</v>
-      </c>
-      <c r="E451" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="452" spans="1:5">
       <c r="A452" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>596</v>
@@ -14791,12 +14791,12 @@
         <v>67</v>
       </c>
       <c r="E452" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="453" spans="1:5">
       <c r="A453" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>596</v>
@@ -14806,12 +14806,12 @@
         <v>510</v>
       </c>
       <c r="E453" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="454" spans="1:5">
       <c r="A454" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>596</v>
@@ -14826,22 +14826,22 @@
     </row>
     <row r="455" spans="1:5">
       <c r="A455" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C455" s="3"/>
       <c r="D455" t="s">
+        <v>656</v>
+      </c>
+      <c r="E455" t="s">
         <v>657</v>
-      </c>
-      <c r="E455" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="456" spans="1:5">
       <c r="A456" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>596</v>
@@ -14851,12 +14851,12 @@
         <v>215</v>
       </c>
       <c r="E456" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="457" spans="1:5">
       <c r="A457" s="26" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>596</v>
@@ -14866,12 +14866,12 @@
         <v>479</v>
       </c>
       <c r="E457" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="458" spans="1:5" ht="16.5">
       <c r="A458" s="25" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>596</v>
@@ -14886,7 +14886,7 @@
     </row>
     <row r="459" spans="1:5" ht="16.5">
       <c r="A459" s="25" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>596</v>
@@ -14896,42 +14896,42 @@
         <v>255</v>
       </c>
       <c r="E459" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="460" spans="1:5" ht="16.5">
       <c r="A460" s="25" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C460" s="3"/>
       <c r="D460" t="s">
+        <v>671</v>
+      </c>
+      <c r="E460" t="s">
         <v>672</v>
-      </c>
-      <c r="E460" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="461" spans="1:5" ht="16.5">
       <c r="A461" s="25" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C461" s="3"/>
       <c r="D461" t="s">
+        <v>673</v>
+      </c>
+      <c r="E461" t="s">
         <v>674</v>
-      </c>
-      <c r="E461" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="462" spans="1:5" ht="16.5">
       <c r="A462" s="25" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>596</v>
@@ -14946,7 +14946,7 @@
     </row>
     <row r="463" spans="1:5" ht="16.5">
       <c r="A463" s="25" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>596</v>
@@ -14961,7 +14961,7 @@
     </row>
     <row r="464" spans="1:5" ht="16.5">
       <c r="A464" s="25" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>596</v>
@@ -14971,12 +14971,12 @@
         <v>67</v>
       </c>
       <c r="E464" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="465" spans="1:5" ht="16.5">
       <c r="A465" s="25" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>596</v>
@@ -14986,27 +14986,27 @@
         <v>270</v>
       </c>
       <c r="E465" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="466" spans="1:5" ht="16.5">
       <c r="A466" s="25" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B466" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C466" s="3"/>
       <c r="D466" t="s">
+        <v>677</v>
+      </c>
+      <c r="E466" t="s">
         <v>678</v>
-      </c>
-      <c r="E466" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="467" spans="1:5" ht="16.5">
       <c r="A467" s="25" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B467" s="3" t="s">
         <v>596</v>
@@ -15016,12 +15016,12 @@
         <v>214</v>
       </c>
       <c r="E467" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="468" spans="1:5" ht="16.5">
       <c r="A468" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B468" s="3" t="s">
         <v>596</v>
@@ -15036,7 +15036,7 @@
     </row>
     <row r="469" spans="1:5" ht="16.5">
       <c r="A469" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B469" s="3" t="s">
         <v>596</v>
@@ -15051,7 +15051,7 @@
     </row>
     <row r="470" spans="1:5" ht="16.5">
       <c r="A470" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B470" s="3" t="s">
         <v>596</v>
@@ -15066,7 +15066,7 @@
     </row>
     <row r="471" spans="1:5" ht="16.5">
       <c r="A471" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B471" s="3" t="s">
         <v>596</v>
@@ -15081,7 +15081,7 @@
     </row>
     <row r="472" spans="1:5" ht="16.5">
       <c r="A472" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B472" s="3" t="s">
         <v>596</v>
@@ -15096,7 +15096,7 @@
     </row>
     <row r="473" spans="1:5" ht="16.5">
       <c r="A473" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B473" s="3" t="s">
         <v>596</v>
@@ -15111,22 +15111,22 @@
     </row>
     <row r="474" spans="1:5" ht="16.5">
       <c r="A474" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C474" s="3"/>
       <c r="D474" t="s">
+        <v>691</v>
+      </c>
+      <c r="E474" t="s">
         <v>692</v>
-      </c>
-      <c r="E474" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="475" spans="1:5" ht="16.5">
       <c r="A475" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B475" s="3" t="s">
         <v>596</v>
@@ -15141,7 +15141,7 @@
     </row>
     <row r="476" spans="1:5" ht="16.5">
       <c r="A476" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B476" s="3" t="s">
         <v>596</v>
@@ -15156,7 +15156,7 @@
     </row>
     <row r="477" spans="1:5" ht="16.5">
       <c r="A477" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B477" s="3" t="s">
         <v>596</v>
@@ -15166,19 +15166,19 @@
         <v>407</v>
       </c>
       <c r="E477" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="478" spans="1:5" ht="16.5">
       <c r="A478" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B478" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C478" s="3"/>
       <c r="D478" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E478" t="s">
         <v>474</v>
@@ -15186,7 +15186,7 @@
     </row>
     <row r="479" spans="1:5" ht="16.5">
       <c r="A479" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B479" s="3" t="s">
         <v>596</v>
@@ -15196,12 +15196,12 @@
         <v>534</v>
       </c>
       <c r="E479" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="480" spans="1:5" ht="16.5">
       <c r="A480" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B480" s="3" t="s">
         <v>596</v>
@@ -15216,22 +15216,22 @@
     </row>
     <row r="481" spans="1:5" ht="16.5">
       <c r="A481" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B481" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C481" s="3"/>
       <c r="D481" t="s">
+        <v>695</v>
+      </c>
+      <c r="E481" t="s">
         <v>696</v>
-      </c>
-      <c r="E481" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="482" spans="1:5" ht="16.5">
       <c r="A482" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B482" s="3" t="s">
         <v>596</v>
@@ -15241,12 +15241,12 @@
         <v>412</v>
       </c>
       <c r="E482" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="483" spans="1:5" ht="16.5">
       <c r="A483" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B483" s="3" t="s">
         <v>596</v>
@@ -15261,7 +15261,7 @@
     </row>
     <row r="484" spans="1:5" ht="16.5">
       <c r="A484" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B484" s="3" t="s">
         <v>596</v>
@@ -15276,7 +15276,7 @@
     </row>
     <row r="485" spans="1:5" ht="16.5">
       <c r="A485" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B485" s="3" t="s">
         <v>596</v>
@@ -15286,12 +15286,12 @@
         <v>415</v>
       </c>
       <c r="E485" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="486" spans="1:5" ht="16.5">
       <c r="A486" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B486" s="3" t="s">
         <v>596</v>
@@ -15301,27 +15301,27 @@
         <v>542</v>
       </c>
       <c r="E486" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="487" spans="1:5" ht="16.5">
       <c r="A487" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B487" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C487" s="3"/>
       <c r="D487" t="s">
+        <v>700</v>
+      </c>
+      <c r="E487" t="s">
         <v>701</v>
-      </c>
-      <c r="E487" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="488" spans="1:5" ht="16.5">
       <c r="A488" s="25" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B488" s="3" t="s">
         <v>596</v>
@@ -15331,12 +15331,12 @@
         <v>416</v>
       </c>
       <c r="E488" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="489" spans="1:5" ht="16.5">
       <c r="A489" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B489" s="3" t="s">
         <v>596</v>
@@ -15351,7 +15351,7 @@
     </row>
     <row r="490" spans="1:5" ht="16.5">
       <c r="A490" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B490" s="3" t="s">
         <v>596</v>
@@ -15366,7 +15366,7 @@
     </row>
     <row r="491" spans="1:5" ht="16.5">
       <c r="A491" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B491" s="3" t="s">
         <v>596</v>
@@ -15381,7 +15381,7 @@
     </row>
     <row r="492" spans="1:5" ht="16.5">
       <c r="A492" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>596</v>
@@ -15396,7 +15396,7 @@
     </row>
     <row r="493" spans="1:5" ht="16.5">
       <c r="A493" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B493" s="3" t="s">
         <v>596</v>
@@ -15411,7 +15411,7 @@
     </row>
     <row r="494" spans="1:5" ht="16.5">
       <c r="A494" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>596</v>
@@ -15426,7 +15426,7 @@
     </row>
     <row r="495" spans="1:5" ht="16.5">
       <c r="A495" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B495" s="3" t="s">
         <v>596</v>
@@ -15436,12 +15436,12 @@
         <v>553</v>
       </c>
       <c r="E495" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="496" spans="1:5" ht="16.5">
       <c r="A496" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B496" s="3" t="s">
         <v>596</v>
@@ -15456,7 +15456,7 @@
     </row>
     <row r="497" spans="1:5" ht="16.5">
       <c r="A497" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B497" s="3" t="s">
         <v>596</v>
@@ -15466,27 +15466,27 @@
         <v>411</v>
       </c>
       <c r="E497" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="498" spans="1:5" ht="16.5">
       <c r="A498" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B498" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C498" s="3"/>
       <c r="D498" t="s">
+        <v>713</v>
+      </c>
+      <c r="E498" t="s">
         <v>714</v>
-      </c>
-      <c r="E498" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="499" spans="1:5" ht="16.5">
       <c r="A499" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B499" s="3" t="s">
         <v>596</v>
@@ -15501,7 +15501,7 @@
     </row>
     <row r="500" spans="1:5" ht="16.5">
       <c r="A500" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B500" s="3" t="s">
         <v>596</v>
@@ -15511,12 +15511,12 @@
         <v>531</v>
       </c>
       <c r="E500" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="501" spans="1:5" ht="16.5">
       <c r="A501" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B501" s="3" t="s">
         <v>596</v>
@@ -15531,7 +15531,7 @@
     </row>
     <row r="502" spans="1:5" ht="16.5">
       <c r="A502" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B502" s="3" t="s">
         <v>596</v>
@@ -15541,12 +15541,12 @@
         <v>534</v>
       </c>
       <c r="E502" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="503" spans="1:5" ht="16.5">
       <c r="A503" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>596</v>
@@ -15561,7 +15561,7 @@
     </row>
     <row r="504" spans="1:5" ht="16.5">
       <c r="A504" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>596</v>
@@ -15571,12 +15571,12 @@
         <v>67</v>
       </c>
       <c r="E504" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="505" spans="1:5" ht="16.5">
       <c r="A505" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>596</v>
@@ -15591,7 +15591,7 @@
     </row>
     <row r="506" spans="1:5" ht="16.5">
       <c r="A506" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>596</v>
@@ -15606,7 +15606,7 @@
     </row>
     <row r="507" spans="1:5" ht="16.5">
       <c r="A507" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B507" s="3" t="s">
         <v>596</v>
@@ -15621,7 +15621,7 @@
     </row>
     <row r="508" spans="1:5" ht="16.5">
       <c r="A508" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B508" s="3" t="s">
         <v>596</v>
@@ -15636,7 +15636,7 @@
     </row>
     <row r="509" spans="1:5" ht="16.5">
       <c r="A509" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B509" s="3" t="s">
         <v>596</v>
@@ -15646,12 +15646,12 @@
         <v>270</v>
       </c>
       <c r="E509" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="510" spans="1:5" ht="16.5">
       <c r="A510" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B510" s="3" t="s">
         <v>596</v>
@@ -15661,12 +15661,12 @@
         <v>542</v>
       </c>
       <c r="E510" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="511" spans="1:5" ht="16.5">
       <c r="A511" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B511" s="3" t="s">
         <v>596</v>
@@ -15676,12 +15676,12 @@
         <v>544</v>
       </c>
       <c r="E511" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="512" spans="1:5" ht="16.5">
       <c r="A512" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B512" s="3" t="s">
         <v>596</v>
@@ -15691,12 +15691,12 @@
         <v>215</v>
       </c>
       <c r="E512" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="513" spans="1:5" ht="16.5">
       <c r="A513" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>596</v>
@@ -15711,7 +15711,7 @@
     </row>
     <row r="514" spans="1:5" ht="16.5">
       <c r="A514" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B514" s="3" t="s">
         <v>596</v>
@@ -15726,7 +15726,7 @@
     </row>
     <row r="515" spans="1:5" ht="16.5">
       <c r="A515" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B515" s="3" t="s">
         <v>596</v>
@@ -15741,7 +15741,7 @@
     </row>
     <row r="516" spans="1:5" ht="16.5">
       <c r="A516" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B516" s="3" t="s">
         <v>596</v>
@@ -15756,7 +15756,7 @@
     </row>
     <row r="517" spans="1:5" ht="16.5">
       <c r="A517" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B517" s="3" t="s">
         <v>596</v>
@@ -15771,7 +15771,7 @@
     </row>
     <row r="518" spans="1:5" ht="16.5">
       <c r="A518" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B518" s="3" t="s">
         <v>596</v>
@@ -15786,7 +15786,7 @@
     </row>
     <row r="519" spans="1:5" ht="16.5">
       <c r="A519" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B519" s="3" t="s">
         <v>596</v>
@@ -15796,12 +15796,12 @@
         <v>528</v>
       </c>
       <c r="E519" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="520" spans="1:5" ht="16.5">
       <c r="A520" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B520" s="3" t="s">
         <v>596</v>
@@ -15816,7 +15816,7 @@
     </row>
     <row r="521" spans="1:5" ht="16.5">
       <c r="A521" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B521" s="3" t="s">
         <v>596</v>
@@ -15826,27 +15826,27 @@
         <v>411</v>
       </c>
       <c r="E521" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="522" spans="1:5" ht="16.5">
       <c r="A522" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B522" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C522" s="3"/>
       <c r="D522" t="s">
+        <v>713</v>
+      </c>
+      <c r="E522" t="s">
         <v>714</v>
-      </c>
-      <c r="E522" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="523" spans="1:5" ht="16.5">
       <c r="A523" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B523" s="3" t="s">
         <v>596</v>
@@ -15861,7 +15861,7 @@
     </row>
     <row r="524" spans="1:5" ht="16.5">
       <c r="A524" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B524" s="3" t="s">
         <v>596</v>
@@ -15871,12 +15871,12 @@
         <v>531</v>
       </c>
       <c r="E524" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="525" spans="1:5" ht="16.5">
       <c r="A525" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B525" s="3" t="s">
         <v>596</v>
@@ -15891,7 +15891,7 @@
     </row>
     <row r="526" spans="1:5" ht="16.5">
       <c r="A526" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B526" s="3" t="s">
         <v>596</v>
@@ -15901,12 +15901,12 @@
         <v>534</v>
       </c>
       <c r="E526" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="527" spans="1:5" ht="16.5">
       <c r="A527" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B527" s="3" t="s">
         <v>596</v>
@@ -15921,7 +15921,7 @@
     </row>
     <row r="528" spans="1:5" ht="16.5">
       <c r="A528" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B528" s="3" t="s">
         <v>596</v>
@@ -15931,12 +15931,12 @@
         <v>67</v>
       </c>
       <c r="E528" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="529" spans="1:5" ht="16.5">
       <c r="A529" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B529" s="3" t="s">
         <v>596</v>
@@ -15951,7 +15951,7 @@
     </row>
     <row r="530" spans="1:5" ht="16.5">
       <c r="A530" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B530" s="3" t="s">
         <v>596</v>
@@ -15966,7 +15966,7 @@
     </row>
     <row r="531" spans="1:5" ht="16.5">
       <c r="A531" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B531" s="3" t="s">
         <v>596</v>
@@ -15981,7 +15981,7 @@
     </row>
     <row r="532" spans="1:5" ht="16.5">
       <c r="A532" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B532" s="3" t="s">
         <v>596</v>
@@ -15996,7 +15996,7 @@
     </row>
     <row r="533" spans="1:5" ht="16.5">
       <c r="A533" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B533" s="3" t="s">
         <v>596</v>
@@ -16011,7 +16011,7 @@
     </row>
     <row r="534" spans="1:5" ht="16.5">
       <c r="A534" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B534" s="3" t="s">
         <v>596</v>
@@ -16021,12 +16021,12 @@
         <v>270</v>
       </c>
       <c r="E534" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="535" spans="1:5" ht="16.5">
       <c r="A535" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B535" s="3" t="s">
         <v>596</v>
@@ -16036,12 +16036,12 @@
         <v>542</v>
       </c>
       <c r="E535" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="536" spans="1:5" ht="16.5">
       <c r="A536" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B536" s="3" t="s">
         <v>596</v>
@@ -16051,12 +16051,12 @@
         <v>544</v>
       </c>
       <c r="E536" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="537" spans="1:5" ht="16.5">
       <c r="A537" s="25" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B537" s="3" t="s">
         <v>596</v>
@@ -16066,12 +16066,12 @@
         <v>215</v>
       </c>
       <c r="E537" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="538" spans="1:5" ht="16.5">
       <c r="A538" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B538" s="3" t="s">
         <v>596</v>
@@ -16081,12 +16081,12 @@
         <v>386</v>
       </c>
       <c r="E538" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="539" spans="1:5" ht="16.5">
       <c r="A539" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B539" s="3" t="s">
         <v>596</v>
@@ -16101,7 +16101,7 @@
     </row>
     <row r="540" spans="1:5" ht="16.5">
       <c r="A540" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B540" s="3" t="s">
         <v>596</v>
@@ -16116,7 +16116,7 @@
     </row>
     <row r="541" spans="1:5" ht="16.5">
       <c r="A541" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B541" s="3" t="s">
         <v>596</v>
@@ -16131,7 +16131,7 @@
     </row>
     <row r="542" spans="1:5" ht="16.5">
       <c r="A542" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B542" s="3" t="s">
         <v>596</v>
@@ -16146,52 +16146,52 @@
     </row>
     <row r="543" spans="1:5" ht="16.5">
       <c r="A543" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B543" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C543" s="3"/>
       <c r="D543" t="s">
+        <v>742</v>
+      </c>
+      <c r="E543" t="s">
         <v>743</v>
-      </c>
-      <c r="E543" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="544" spans="1:5" ht="16.5">
       <c r="A544" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B544" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C544" s="3"/>
       <c r="D544" t="s">
+        <v>744</v>
+      </c>
+      <c r="E544" t="s">
         <v>745</v>
-      </c>
-      <c r="E544" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="545" spans="1:5" ht="16.5">
       <c r="A545" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B545" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C545" s="3"/>
       <c r="D545" t="s">
+        <v>746</v>
+      </c>
+      <c r="E545" t="s">
         <v>747</v>
-      </c>
-      <c r="E545" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="546" spans="1:5" ht="16.5">
       <c r="A546" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B546" s="3" t="s">
         <v>596</v>
@@ -16206,7 +16206,7 @@
     </row>
     <row r="547" spans="1:5" ht="16.5">
       <c r="A547" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B547" s="3" t="s">
         <v>596</v>
@@ -16221,7 +16221,7 @@
     </row>
     <row r="548" spans="1:5" ht="16.5">
       <c r="A548" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B548" s="3" t="s">
         <v>596</v>
@@ -16231,42 +16231,42 @@
         <v>531</v>
       </c>
       <c r="E548" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="549" spans="1:5" ht="16.5">
       <c r="A549" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B549" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C549" s="3"/>
       <c r="D549" t="s">
+        <v>749</v>
+      </c>
+      <c r="E549" t="s">
         <v>750</v>
-      </c>
-      <c r="E549" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="550" spans="1:5" ht="16.5">
       <c r="A550" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B550" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C550" s="3"/>
       <c r="D550" t="s">
+        <v>751</v>
+      </c>
+      <c r="E550" t="s">
         <v>752</v>
-      </c>
-      <c r="E550" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="551" spans="1:5" ht="16.5">
       <c r="A551" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B551" s="3" t="s">
         <v>596</v>
@@ -16276,12 +16276,12 @@
         <v>67</v>
       </c>
       <c r="E551" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="552" spans="1:5" ht="16.5">
       <c r="A552" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B552" s="3" t="s">
         <v>596</v>
@@ -16296,14 +16296,14 @@
     </row>
     <row r="553" spans="1:5" ht="16.5">
       <c r="A553" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B553" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C553" s="3"/>
       <c r="D553" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E553" t="s">
         <v>421</v>
@@ -16311,7 +16311,7 @@
     </row>
     <row r="554" spans="1:5" ht="16.5">
       <c r="A554" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B554" s="3" t="s">
         <v>596</v>
@@ -16321,12 +16321,12 @@
         <v>270</v>
       </c>
       <c r="E554" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="555" spans="1:5" ht="16.5">
       <c r="A555" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B555" s="3" t="s">
         <v>596</v>
@@ -16336,12 +16336,12 @@
         <v>532</v>
       </c>
       <c r="E555" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="556" spans="1:5" ht="16.5">
       <c r="A556" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B556" s="3" t="s">
         <v>596</v>
@@ -16351,12 +16351,12 @@
         <v>214</v>
       </c>
       <c r="E556" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="557" spans="1:5" ht="16.5">
       <c r="A557" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B557" s="3" t="s">
         <v>596</v>
@@ -16366,12 +16366,12 @@
         <v>416</v>
       </c>
       <c r="E557" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="558" spans="1:5" ht="16.5">
       <c r="A558" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B558" s="3" t="s">
         <v>596</v>
@@ -16386,7 +16386,7 @@
     </row>
     <row r="559" spans="1:5" ht="16.5">
       <c r="A559" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B559" s="3" t="s">
         <v>596</v>
@@ -16401,7 +16401,7 @@
     </row>
     <row r="560" spans="1:5" ht="16.5">
       <c r="A560" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B560" s="3" t="s">
         <v>596</v>
@@ -16416,7 +16416,7 @@
     </row>
     <row r="561" spans="1:5" ht="16.5">
       <c r="A561" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B561" s="3" t="s">
         <v>596</v>
@@ -16431,7 +16431,7 @@
     </row>
     <row r="562" spans="1:5" ht="16.5">
       <c r="A562" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B562" s="3" t="s">
         <v>596</v>
@@ -16446,7 +16446,7 @@
     </row>
     <row r="563" spans="1:5" ht="16.5">
       <c r="A563" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B563" s="3" t="s">
         <v>596</v>
@@ -16461,52 +16461,52 @@
     </row>
     <row r="564" spans="1:5" ht="16.5">
       <c r="A564" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B564" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C564" s="3"/>
       <c r="D564" t="s">
+        <v>775</v>
+      </c>
+      <c r="E564" t="s">
         <v>776</v>
-      </c>
-      <c r="E564" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="565" spans="1:5" ht="16.5">
       <c r="A565" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B565" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C565" s="3"/>
       <c r="D565" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E565" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="566" spans="1:5" ht="16.5">
       <c r="A566" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B566" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C566" s="3"/>
       <c r="D566" t="s">
+        <v>778</v>
+      </c>
+      <c r="E566" t="s">
         <v>779</v>
-      </c>
-      <c r="E566" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="567" spans="1:5" ht="16.5">
       <c r="A567" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B567" s="3" t="s">
         <v>596</v>
@@ -16516,42 +16516,42 @@
         <v>406</v>
       </c>
       <c r="E567" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="568" spans="1:5" ht="16.5">
       <c r="A568" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B568" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C568" s="3"/>
       <c r="D568" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E568" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="569" spans="1:5" ht="16.5">
       <c r="A569" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B569" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C569" s="3"/>
       <c r="D569" t="s">
+        <v>782</v>
+      </c>
+      <c r="E569" t="s">
         <v>783</v>
-      </c>
-      <c r="E569" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="570" spans="1:5" ht="16.5">
       <c r="A570" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B570" s="3" t="s">
         <v>596</v>
@@ -16566,7 +16566,7 @@
     </row>
     <row r="571" spans="1:5" ht="16.5">
       <c r="A571" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B571" s="3" t="s">
         <v>596</v>
@@ -16581,7 +16581,7 @@
     </row>
     <row r="572" spans="1:5" ht="16.5">
       <c r="A572" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B572" s="3" t="s">
         <v>596</v>
@@ -16591,12 +16591,12 @@
         <v>472</v>
       </c>
       <c r="E572" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="573" spans="1:5" ht="16.5">
       <c r="A573" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B573" s="3" t="s">
         <v>596</v>
@@ -16606,27 +16606,27 @@
         <v>262</v>
       </c>
       <c r="E573" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="574" spans="1:5" ht="16.5">
       <c r="A574" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B574" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C574" s="3"/>
       <c r="D574" t="s">
+        <v>785</v>
+      </c>
+      <c r="E574" t="s">
         <v>786</v>
-      </c>
-      <c r="E574" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="575" spans="1:5" ht="16.5">
       <c r="A575" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B575" s="3" t="s">
         <v>596</v>
@@ -16636,12 +16636,12 @@
         <v>473</v>
       </c>
       <c r="E575" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="576" spans="1:5" ht="16.5">
       <c r="A576" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B576" s="3" t="s">
         <v>596</v>
@@ -16656,22 +16656,22 @@
     </row>
     <row r="577" spans="1:5" ht="16.5">
       <c r="A577" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B577" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C577" s="3"/>
       <c r="D577" t="s">
+        <v>788</v>
+      </c>
+      <c r="E577" t="s">
         <v>789</v>
-      </c>
-      <c r="E577" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="578" spans="1:5" ht="16.5">
       <c r="A578" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B578" s="3" t="s">
         <v>596</v>
@@ -16681,27 +16681,27 @@
         <v>67</v>
       </c>
       <c r="E578" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="579" spans="1:5" ht="16.5">
       <c r="A579" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B579" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C579" s="3"/>
       <c r="D579" t="s">
+        <v>791</v>
+      </c>
+      <c r="E579" t="s">
         <v>792</v>
-      </c>
-      <c r="E579" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="580" spans="1:5" ht="16.5">
       <c r="A580" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B580" s="3" t="s">
         <v>596</v>
@@ -16716,7 +16716,7 @@
     </row>
     <row r="581" spans="1:5" ht="16.5">
       <c r="A581" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B581" s="3" t="s">
         <v>596</v>
@@ -16726,12 +16726,12 @@
         <v>413</v>
       </c>
       <c r="E581" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="582" spans="1:5" ht="16.5">
       <c r="A582" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B582" s="3" t="s">
         <v>596</v>
@@ -16746,7 +16746,7 @@
     </row>
     <row r="583" spans="1:5" ht="16.5">
       <c r="A583" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B583" s="3" t="s">
         <v>596</v>
@@ -16761,7 +16761,7 @@
     </row>
     <row r="584" spans="1:5" ht="16.5">
       <c r="A584" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B584" s="3" t="s">
         <v>596</v>
@@ -16776,7 +16776,7 @@
     </row>
     <row r="585" spans="1:5" ht="16.5">
       <c r="A585" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B585" s="3" t="s">
         <v>596</v>
@@ -16786,12 +16786,12 @@
         <v>214</v>
       </c>
       <c r="E585" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="586" spans="1:5" ht="16.5">
       <c r="A586" s="25" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B586" s="3" t="s">
         <v>596</v>
@@ -16801,12 +16801,12 @@
         <v>215</v>
       </c>
       <c r="E586" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="587" spans="1:5" ht="16.5">
       <c r="A587" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B587" s="3" t="s">
         <v>596</v>
@@ -16821,7 +16821,7 @@
     </row>
     <row r="588" spans="1:5" ht="16.5">
       <c r="A588" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B588" s="3" t="s">
         <v>596</v>
@@ -16836,7 +16836,7 @@
     </row>
     <row r="589" spans="1:5" ht="16.5">
       <c r="A589" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B589" s="3" t="s">
         <v>596</v>
@@ -16851,7 +16851,7 @@
     </row>
     <row r="590" spans="1:5" ht="16.5">
       <c r="A590" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B590" s="3" t="s">
         <v>596</v>
@@ -16866,7 +16866,7 @@
     </row>
     <row r="591" spans="1:5" ht="16.5">
       <c r="A591" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B591" s="3" t="s">
         <v>596</v>
@@ -16881,7 +16881,7 @@
     </row>
     <row r="592" spans="1:5" ht="16.5">
       <c r="A592" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B592" s="3" t="s">
         <v>596</v>
@@ -16896,52 +16896,52 @@
     </row>
     <row r="593" spans="1:5" ht="16.5">
       <c r="A593" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B593" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C593" s="3"/>
       <c r="D593" t="s">
+        <v>775</v>
+      </c>
+      <c r="E593" t="s">
         <v>776</v>
-      </c>
-      <c r="E593" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="594" spans="1:5" ht="16.5">
       <c r="A594" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B594" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C594" s="3"/>
       <c r="D594" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E594" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="595" spans="1:5" ht="16.5">
       <c r="A595" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B595" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C595" s="3"/>
       <c r="D595" t="s">
+        <v>778</v>
+      </c>
+      <c r="E595" t="s">
         <v>779</v>
-      </c>
-      <c r="E595" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="596" spans="1:5" ht="16.5">
       <c r="A596" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B596" s="3" t="s">
         <v>596</v>
@@ -16951,42 +16951,42 @@
         <v>406</v>
       </c>
       <c r="E596" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="597" spans="1:5" ht="16.5">
       <c r="A597" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B597" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C597" s="3"/>
       <c r="D597" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E597" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="598" spans="1:5" ht="16.5">
       <c r="A598" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B598" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C598" s="3"/>
       <c r="D598" t="s">
+        <v>782</v>
+      </c>
+      <c r="E598" t="s">
         <v>783</v>
-      </c>
-      <c r="E598" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="599" spans="1:5" ht="16.5">
       <c r="A599" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B599" s="3" t="s">
         <v>596</v>
@@ -17001,7 +17001,7 @@
     </row>
     <row r="600" spans="1:5" ht="16.5">
       <c r="A600" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B600" s="3" t="s">
         <v>596</v>
@@ -17016,7 +17016,7 @@
     </row>
     <row r="601" spans="1:5" ht="16.5">
       <c r="A601" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B601" s="3" t="s">
         <v>596</v>
@@ -17026,12 +17026,12 @@
         <v>472</v>
       </c>
       <c r="E601" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="602" spans="1:5" ht="16.5">
       <c r="A602" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B602" s="3" t="s">
         <v>596</v>
@@ -17041,27 +17041,27 @@
         <v>262</v>
       </c>
       <c r="E602" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="603" spans="1:5" ht="16.5">
       <c r="A603" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B603" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C603" s="3"/>
       <c r="D603" t="s">
+        <v>785</v>
+      </c>
+      <c r="E603" t="s">
         <v>786</v>
-      </c>
-      <c r="E603" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="604" spans="1:5" ht="16.5">
       <c r="A604" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B604" s="3" t="s">
         <v>596</v>
@@ -17071,12 +17071,12 @@
         <v>473</v>
       </c>
       <c r="E604" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="605" spans="1:5" ht="16.5">
       <c r="A605" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B605" s="3" t="s">
         <v>596</v>
@@ -17091,22 +17091,22 @@
     </row>
     <row r="606" spans="1:5" ht="16.5">
       <c r="A606" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B606" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C606" s="3"/>
       <c r="D606" t="s">
+        <v>788</v>
+      </c>
+      <c r="E606" t="s">
         <v>789</v>
-      </c>
-      <c r="E606" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="607" spans="1:5" ht="16.5">
       <c r="A607" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B607" s="3" t="s">
         <v>596</v>
@@ -17116,27 +17116,27 @@
         <v>67</v>
       </c>
       <c r="E607" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="608" spans="1:5" ht="16.5">
       <c r="A608" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B608" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C608" s="3"/>
       <c r="D608" t="s">
+        <v>791</v>
+      </c>
+      <c r="E608" t="s">
         <v>792</v>
-      </c>
-      <c r="E608" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="609" spans="1:5" ht="16.5">
       <c r="A609" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B609" s="3" t="s">
         <v>596</v>
@@ -17151,7 +17151,7 @@
     </row>
     <row r="610" spans="1:5" ht="16.5">
       <c r="A610" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B610" s="3" t="s">
         <v>596</v>
@@ -17161,12 +17161,12 @@
         <v>413</v>
       </c>
       <c r="E610" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="611" spans="1:5" ht="16.5">
       <c r="A611" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B611" s="3" t="s">
         <v>596</v>
@@ -17181,7 +17181,7 @@
     </row>
     <row r="612" spans="1:5" ht="16.5">
       <c r="A612" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B612" s="3" t="s">
         <v>596</v>
@@ -17196,7 +17196,7 @@
     </row>
     <row r="613" spans="1:5" ht="16.5">
       <c r="A613" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B613" s="3" t="s">
         <v>596</v>
@@ -17211,7 +17211,7 @@
     </row>
     <row r="614" spans="1:5" ht="16.5">
       <c r="A614" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B614" s="3" t="s">
         <v>596</v>
@@ -17221,12 +17221,12 @@
         <v>214</v>
       </c>
       <c r="E614" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="615" spans="1:5" ht="16.5">
       <c r="A615" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B615" s="3" t="s">
         <v>596</v>
@@ -17236,12 +17236,12 @@
         <v>215</v>
       </c>
       <c r="E615" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="616" spans="1:5" ht="16.5">
       <c r="A616" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B616" s="3" t="s">
         <v>596</v>
@@ -17256,7 +17256,7 @@
     </row>
     <row r="617" spans="1:5" ht="16.5">
       <c r="A617" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B617" s="3" t="s">
         <v>596</v>
@@ -17271,7 +17271,7 @@
     </row>
     <row r="618" spans="1:5" ht="16.5">
       <c r="A618" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B618" s="3" t="s">
         <v>596</v>
@@ -17286,7 +17286,7 @@
     </row>
     <row r="619" spans="1:5" ht="16.5">
       <c r="A619" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B619" s="3" t="s">
         <v>596</v>
@@ -17301,7 +17301,7 @@
     </row>
     <row r="620" spans="1:5" ht="16.5">
       <c r="A620" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B620" s="3" t="s">
         <v>596</v>
@@ -17316,7 +17316,7 @@
     </row>
     <row r="621" spans="1:5" ht="16.5">
       <c r="A621" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B621" s="3" t="s">
         <v>596</v>
@@ -17331,52 +17331,52 @@
     </row>
     <row r="622" spans="1:5" ht="16.5">
       <c r="A622" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B622" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C622" s="3"/>
       <c r="D622" t="s">
+        <v>775</v>
+      </c>
+      <c r="E622" t="s">
         <v>776</v>
-      </c>
-      <c r="E622" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="623" spans="1:5" ht="16.5">
       <c r="A623" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B623" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C623" s="3"/>
       <c r="D623" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E623" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="624" spans="1:5" ht="16.5">
       <c r="A624" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B624" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C624" s="3"/>
       <c r="D624" t="s">
+        <v>778</v>
+      </c>
+      <c r="E624" t="s">
         <v>779</v>
-      </c>
-      <c r="E624" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="625" spans="1:5" ht="16.5">
       <c r="A625" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B625" s="3" t="s">
         <v>596</v>
@@ -17386,42 +17386,42 @@
         <v>406</v>
       </c>
       <c r="E625" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="626" spans="1:5" ht="16.5">
       <c r="A626" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B626" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C626" s="3"/>
       <c r="D626" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E626" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="627" spans="1:5" ht="16.5">
       <c r="A627" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B627" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C627" s="3"/>
       <c r="D627" t="s">
+        <v>782</v>
+      </c>
+      <c r="E627" t="s">
         <v>783</v>
-      </c>
-      <c r="E627" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="628" spans="1:5" ht="16.5">
       <c r="A628" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B628" s="3" t="s">
         <v>596</v>
@@ -17436,7 +17436,7 @@
     </row>
     <row r="629" spans="1:5" ht="16.5">
       <c r="A629" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B629" s="3" t="s">
         <v>596</v>
@@ -17451,7 +17451,7 @@
     </row>
     <row r="630" spans="1:5" ht="16.5">
       <c r="A630" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B630" s="3" t="s">
         <v>596</v>
@@ -17461,12 +17461,12 @@
         <v>472</v>
       </c>
       <c r="E630" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="631" spans="1:5" ht="16.5">
       <c r="A631" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B631" s="3" t="s">
         <v>596</v>
@@ -17476,27 +17476,27 @@
         <v>262</v>
       </c>
       <c r="E631" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="632" spans="1:5" ht="16.5">
       <c r="A632" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B632" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C632" s="3"/>
       <c r="D632" t="s">
+        <v>785</v>
+      </c>
+      <c r="E632" t="s">
         <v>786</v>
-      </c>
-      <c r="E632" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="633" spans="1:5" ht="16.5">
       <c r="A633" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B633" s="3" t="s">
         <v>596</v>
@@ -17506,12 +17506,12 @@
         <v>473</v>
       </c>
       <c r="E633" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="634" spans="1:5" ht="16.5">
       <c r="A634" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B634" s="3" t="s">
         <v>596</v>
@@ -17526,22 +17526,22 @@
     </row>
     <row r="635" spans="1:5" ht="16.5">
       <c r="A635" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B635" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C635" s="3"/>
       <c r="D635" t="s">
+        <v>788</v>
+      </c>
+      <c r="E635" t="s">
         <v>789</v>
-      </c>
-      <c r="E635" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="636" spans="1:5" ht="16.5">
       <c r="A636" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B636" s="3" t="s">
         <v>596</v>
@@ -17551,27 +17551,27 @@
         <v>67</v>
       </c>
       <c r="E636" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="637" spans="1:5" ht="16.5">
       <c r="A637" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B637" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C637" s="3"/>
       <c r="D637" t="s">
+        <v>791</v>
+      </c>
+      <c r="E637" t="s">
         <v>792</v>
-      </c>
-      <c r="E637" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="638" spans="1:5" ht="16.5">
       <c r="A638" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B638" s="3" t="s">
         <v>596</v>
@@ -17586,7 +17586,7 @@
     </row>
     <row r="639" spans="1:5" ht="16.5">
       <c r="A639" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B639" s="3" t="s">
         <v>596</v>
@@ -17596,12 +17596,12 @@
         <v>413</v>
       </c>
       <c r="E639" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="640" spans="1:5" ht="16.5">
       <c r="A640" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B640" s="3" t="s">
         <v>596</v>
@@ -17616,7 +17616,7 @@
     </row>
     <row r="641" spans="1:5" ht="16.5">
       <c r="A641" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B641" s="3" t="s">
         <v>596</v>
@@ -17631,7 +17631,7 @@
     </row>
     <row r="642" spans="1:5" ht="16.5">
       <c r="A642" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B642" s="3" t="s">
         <v>596</v>
@@ -17646,7 +17646,7 @@
     </row>
     <row r="643" spans="1:5" ht="16.5">
       <c r="A643" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B643" s="3" t="s">
         <v>596</v>
@@ -17656,12 +17656,12 @@
         <v>214</v>
       </c>
       <c r="E643" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="644" spans="1:5" ht="16.5">
       <c r="A644" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B644" s="3" t="s">
         <v>596</v>
@@ -17671,12 +17671,12 @@
         <v>215</v>
       </c>
       <c r="E644" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="645" spans="1:5" ht="16.5">
       <c r="A645" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B645" s="3" t="s">
         <v>596</v>
@@ -17691,7 +17691,7 @@
     </row>
     <row r="646" spans="1:5" ht="16.5">
       <c r="A646" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B646" s="3" t="s">
         <v>596</v>
@@ -17706,7 +17706,7 @@
     </row>
     <row r="647" spans="1:5" ht="16.5">
       <c r="A647" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B647" s="3" t="s">
         <v>596</v>
@@ -17721,7 +17721,7 @@
     </row>
     <row r="648" spans="1:5" ht="16.5">
       <c r="A648" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B648" s="3" t="s">
         <v>596</v>
@@ -17736,7 +17736,7 @@
     </row>
     <row r="649" spans="1:5" ht="16.5">
       <c r="A649" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B649" s="3" t="s">
         <v>596</v>
@@ -17751,7 +17751,7 @@
     </row>
     <row r="650" spans="1:5" ht="16.5">
       <c r="A650" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B650" s="3" t="s">
         <v>596</v>
@@ -17766,52 +17766,52 @@
     </row>
     <row r="651" spans="1:5" ht="16.5">
       <c r="A651" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B651" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C651" s="3"/>
       <c r="D651" t="s">
+        <v>775</v>
+      </c>
+      <c r="E651" t="s">
         <v>776</v>
-      </c>
-      <c r="E651" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="652" spans="1:5" ht="16.5">
       <c r="A652" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B652" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C652" s="3"/>
       <c r="D652" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E652" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="653" spans="1:5" ht="16.5">
       <c r="A653" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B653" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C653" s="3"/>
       <c r="D653" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E653" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="654" spans="1:5" ht="16.5">
       <c r="A654" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B654" s="3" t="s">
         <v>596</v>
@@ -17821,42 +17821,42 @@
         <v>406</v>
       </c>
       <c r="E654" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="655" spans="1:5" ht="16.5">
       <c r="A655" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B655" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C655" s="3"/>
       <c r="D655" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E655" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="656" spans="1:5" ht="16.5">
       <c r="A656" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B656" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C656" s="3"/>
       <c r="D656" t="s">
+        <v>782</v>
+      </c>
+      <c r="E656" t="s">
         <v>783</v>
-      </c>
-      <c r="E656" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="657" spans="1:5" ht="16.5">
       <c r="A657" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B657" s="3" t="s">
         <v>596</v>
@@ -17871,7 +17871,7 @@
     </row>
     <row r="658" spans="1:5" ht="16.5">
       <c r="A658" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B658" s="3" t="s">
         <v>596</v>
@@ -17886,7 +17886,7 @@
     </row>
     <row r="659" spans="1:5" ht="16.5">
       <c r="A659" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B659" s="3" t="s">
         <v>596</v>
@@ -17896,12 +17896,12 @@
         <v>472</v>
       </c>
       <c r="E659" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="660" spans="1:5" ht="16.5">
       <c r="A660" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B660" s="3" t="s">
         <v>596</v>
@@ -17911,27 +17911,27 @@
         <v>262</v>
       </c>
       <c r="E660" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="661" spans="1:5" ht="16.5">
       <c r="A661" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B661" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C661" s="3"/>
       <c r="D661" t="s">
+        <v>785</v>
+      </c>
+      <c r="E661" t="s">
         <v>786</v>
-      </c>
-      <c r="E661" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="662" spans="1:5" ht="16.5">
       <c r="A662" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B662" s="3" t="s">
         <v>596</v>
@@ -17941,12 +17941,12 @@
         <v>473</v>
       </c>
       <c r="E662" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="663" spans="1:5" ht="16.5">
       <c r="A663" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B663" s="3" t="s">
         <v>596</v>
@@ -17961,22 +17961,22 @@
     </row>
     <row r="664" spans="1:5" ht="16.5">
       <c r="A664" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B664" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C664" s="3"/>
       <c r="D664" t="s">
+        <v>788</v>
+      </c>
+      <c r="E664" t="s">
         <v>789</v>
-      </c>
-      <c r="E664" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="665" spans="1:5" ht="16.5">
       <c r="A665" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B665" s="3" t="s">
         <v>596</v>
@@ -17986,27 +17986,27 @@
         <v>67</v>
       </c>
       <c r="E665" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="666" spans="1:5" ht="16.5">
       <c r="A666" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B666" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C666" s="3"/>
       <c r="D666" t="s">
+        <v>791</v>
+      </c>
+      <c r="E666" t="s">
         <v>792</v>
-      </c>
-      <c r="E666" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="667" spans="1:5" ht="16.5">
       <c r="A667" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B667" s="3" t="s">
         <v>596</v>
@@ -18021,7 +18021,7 @@
     </row>
     <row r="668" spans="1:5" ht="16.5">
       <c r="A668" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B668" s="3" t="s">
         <v>596</v>
@@ -18031,12 +18031,12 @@
         <v>413</v>
       </c>
       <c r="E668" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="669" spans="1:5" ht="16.5">
       <c r="A669" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B669" s="3" t="s">
         <v>596</v>
@@ -18051,7 +18051,7 @@
     </row>
     <row r="670" spans="1:5" ht="16.5">
       <c r="A670" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B670" s="3" t="s">
         <v>596</v>
@@ -18066,7 +18066,7 @@
     </row>
     <row r="671" spans="1:5" ht="16.5">
       <c r="A671" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B671" s="3" t="s">
         <v>596</v>
@@ -18081,7 +18081,7 @@
     </row>
     <row r="672" spans="1:5" ht="16.5">
       <c r="A672" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B672" s="3" t="s">
         <v>596</v>
@@ -18091,12 +18091,12 @@
         <v>214</v>
       </c>
       <c r="E672" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="673" spans="1:5" ht="16.5">
       <c r="A673" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B673" s="3" t="s">
         <v>596</v>
@@ -18106,12 +18106,12 @@
         <v>215</v>
       </c>
       <c r="E673" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="674" spans="1:5" ht="16.5">
       <c r="A674" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B674" s="3" t="s">
         <v>596</v>
@@ -18121,12 +18121,12 @@
         <v>499</v>
       </c>
       <c r="E674" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="675" spans="1:5" ht="16.5">
       <c r="A675" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B675" s="3" t="s">
         <v>596</v>
@@ -18141,7 +18141,7 @@
     </row>
     <row r="676" spans="1:5" ht="16.5">
       <c r="A676" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B676" s="3" t="s">
         <v>596</v>
@@ -18156,7 +18156,7 @@
     </row>
     <row r="677" spans="1:5" ht="16.5">
       <c r="A677" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B677" s="3" t="s">
         <v>596</v>
@@ -18171,7 +18171,7 @@
     </row>
     <row r="678" spans="1:5" ht="16.5">
       <c r="A678" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B678" s="3" t="s">
         <v>596</v>
@@ -18186,7 +18186,7 @@
     </row>
     <row r="679" spans="1:5" ht="16.5">
       <c r="A679" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B679" s="3" t="s">
         <v>596</v>
@@ -18201,7 +18201,7 @@
     </row>
     <row r="680" spans="1:5" ht="16.5">
       <c r="A680" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B680" s="3" t="s">
         <v>596</v>
@@ -18216,7 +18216,7 @@
     </row>
     <row r="681" spans="1:5" ht="16.5">
       <c r="A681" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B681" s="3" t="s">
         <v>596</v>
@@ -18231,7 +18231,7 @@
     </row>
     <row r="682" spans="1:5" ht="16.5">
       <c r="A682" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B682" s="3" t="s">
         <v>596</v>
@@ -18241,12 +18241,12 @@
         <v>531</v>
       </c>
       <c r="E682" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="683" spans="1:5" ht="16.5">
       <c r="A683" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B683" s="3" t="s">
         <v>596</v>
@@ -18256,12 +18256,12 @@
         <v>532</v>
       </c>
       <c r="E683" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="684" spans="1:5" ht="16.5">
       <c r="A684" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B684" s="3" t="s">
         <v>596</v>
@@ -18271,12 +18271,12 @@
         <v>534</v>
       </c>
       <c r="E684" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="685" spans="1:5" ht="16.5">
       <c r="A685" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B685" s="3" t="s">
         <v>596</v>
@@ -18286,12 +18286,12 @@
         <v>536</v>
       </c>
       <c r="E685" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="686" spans="1:5" ht="16.5">
       <c r="A686" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B686" s="3" t="s">
         <v>596</v>
@@ -18301,12 +18301,12 @@
         <v>67</v>
       </c>
       <c r="E686" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="687" spans="1:5" ht="16.5">
       <c r="A687" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B687" s="3" t="s">
         <v>596</v>
@@ -18321,14 +18321,14 @@
     </row>
     <row r="688" spans="1:5" ht="16.5">
       <c r="A688" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B688" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C688" s="3"/>
       <c r="D688" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E688" t="s">
         <v>421</v>
@@ -18336,7 +18336,7 @@
     </row>
     <row r="689" spans="1:5" ht="16.5">
       <c r="A689" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B689" s="3" t="s">
         <v>596</v>
@@ -18346,12 +18346,12 @@
         <v>270</v>
       </c>
       <c r="E689" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="690" spans="1:5" ht="16.5">
       <c r="A690" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B690" s="3" t="s">
         <v>596</v>
@@ -18361,12 +18361,12 @@
         <v>214</v>
       </c>
       <c r="E690" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="691" spans="1:5" ht="16.5">
       <c r="A691" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B691" s="3" t="s">
         <v>596</v>
@@ -18376,12 +18376,12 @@
         <v>215</v>
       </c>
       <c r="E691" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="692" spans="1:5" ht="16.5">
       <c r="A692" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B692" s="3" t="s">
         <v>596</v>
@@ -18391,12 +18391,12 @@
         <v>499</v>
       </c>
       <c r="E692" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="693" spans="1:5" ht="16.5">
       <c r="A693" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B693" s="3" t="s">
         <v>596</v>
@@ -18411,7 +18411,7 @@
     </row>
     <row r="694" spans="1:5" ht="16.5">
       <c r="A694" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B694" s="3" t="s">
         <v>596</v>
@@ -18426,7 +18426,7 @@
     </row>
     <row r="695" spans="1:5" ht="16.5">
       <c r="A695" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B695" s="3" t="s">
         <v>596</v>
@@ -18441,7 +18441,7 @@
     </row>
     <row r="696" spans="1:5" ht="16.5">
       <c r="A696" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B696" s="3" t="s">
         <v>596</v>
@@ -18456,7 +18456,7 @@
     </row>
     <row r="697" spans="1:5" ht="16.5">
       <c r="A697" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B697" s="3" t="s">
         <v>596</v>
@@ -18471,7 +18471,7 @@
     </row>
     <row r="698" spans="1:5" ht="16.5">
       <c r="A698" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B698" s="3" t="s">
         <v>596</v>
@@ -18486,7 +18486,7 @@
     </row>
     <row r="699" spans="1:5" ht="16.5">
       <c r="A699" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B699" s="3" t="s">
         <v>596</v>
@@ -18501,7 +18501,7 @@
     </row>
     <row r="700" spans="1:5" ht="16.5">
       <c r="A700" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B700" s="3" t="s">
         <v>596</v>
@@ -18511,12 +18511,12 @@
         <v>531</v>
       </c>
       <c r="E700" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="701" spans="1:5" ht="16.5">
       <c r="A701" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B701" s="3" t="s">
         <v>596</v>
@@ -18526,12 +18526,12 @@
         <v>532</v>
       </c>
       <c r="E701" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="702" spans="1:5" ht="16.5">
       <c r="A702" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B702" s="3" t="s">
         <v>596</v>
@@ -18541,12 +18541,12 @@
         <v>534</v>
       </c>
       <c r="E702" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="703" spans="1:5" ht="16.5">
       <c r="A703" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B703" s="3" t="s">
         <v>596</v>
@@ -18556,12 +18556,12 @@
         <v>536</v>
       </c>
       <c r="E703" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="704" spans="1:5" ht="16.5">
       <c r="A704" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B704" s="3" t="s">
         <v>596</v>
@@ -18571,12 +18571,12 @@
         <v>67</v>
       </c>
       <c r="E704" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="705" spans="1:5" ht="16.5">
       <c r="A705" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B705" s="3" t="s">
         <v>596</v>
@@ -18591,14 +18591,14 @@
     </row>
     <row r="706" spans="1:5" ht="16.5">
       <c r="A706" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B706" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C706" s="3"/>
       <c r="D706" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E706" t="s">
         <v>421</v>
@@ -18606,7 +18606,7 @@
     </row>
     <row r="707" spans="1:5" ht="16.5">
       <c r="A707" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B707" s="3" t="s">
         <v>596</v>
@@ -18616,12 +18616,12 @@
         <v>270</v>
       </c>
       <c r="E707" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="708" spans="1:5" ht="16.5">
       <c r="A708" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B708" s="3" t="s">
         <v>596</v>
@@ -18631,12 +18631,12 @@
         <v>214</v>
       </c>
       <c r="E708" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="709" spans="1:5" ht="16.5">
       <c r="A709" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B709" s="3" t="s">
         <v>596</v>
@@ -18646,12 +18646,12 @@
         <v>215</v>
       </c>
       <c r="E709" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="710" spans="1:5" ht="16.5">
       <c r="A710" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B710" s="3" t="s">
         <v>596</v>
@@ -18661,12 +18661,12 @@
         <v>499</v>
       </c>
       <c r="E710" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="711" spans="1:5" ht="16.5">
       <c r="A711" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B711" s="3" t="s">
         <v>596</v>
@@ -18681,7 +18681,7 @@
     </row>
     <row r="712" spans="1:5" ht="16.5">
       <c r="A712" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B712" s="3" t="s">
         <v>596</v>
@@ -18696,7 +18696,7 @@
     </row>
     <row r="713" spans="1:5" ht="16.5">
       <c r="A713" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B713" s="3" t="s">
         <v>596</v>
@@ -18711,7 +18711,7 @@
     </row>
     <row r="714" spans="1:5" ht="16.5">
       <c r="A714" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B714" s="3" t="s">
         <v>596</v>
@@ -18726,7 +18726,7 @@
     </row>
     <row r="715" spans="1:5" ht="16.5">
       <c r="A715" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B715" s="3" t="s">
         <v>596</v>
@@ -18741,14 +18741,14 @@
     </row>
     <row r="716" spans="1:5" ht="16.5">
       <c r="A716" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B716" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C716" s="3"/>
       <c r="D716" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E716" t="s">
         <v>504</v>
@@ -18756,7 +18756,7 @@
     </row>
     <row r="717" spans="1:5" ht="16.5">
       <c r="A717" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B717" s="3" t="s">
         <v>596</v>
@@ -18766,12 +18766,12 @@
         <v>406</v>
       </c>
       <c r="E717" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="718" spans="1:5" ht="16.5">
       <c r="A718" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B718" s="3" t="s">
         <v>596</v>
@@ -18786,7 +18786,7 @@
     </row>
     <row r="719" spans="1:5" ht="16.5">
       <c r="A719" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B719" s="3" t="s">
         <v>596</v>
@@ -18796,12 +18796,12 @@
         <v>531</v>
       </c>
       <c r="E719" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="720" spans="1:5" ht="16.5">
       <c r="A720" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B720" s="3" t="s">
         <v>596</v>
@@ -18811,12 +18811,12 @@
         <v>532</v>
       </c>
       <c r="E720" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="721" spans="1:5" ht="16.5">
       <c r="A721" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B721" s="3" t="s">
         <v>596</v>
@@ -18826,12 +18826,12 @@
         <v>534</v>
       </c>
       <c r="E721" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="722" spans="1:5" ht="16.5">
       <c r="A722" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B722" s="3" t="s">
         <v>596</v>
@@ -18841,12 +18841,12 @@
         <v>536</v>
       </c>
       <c r="E722" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="723" spans="1:5" ht="16.5">
       <c r="A723" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B723" s="3" t="s">
         <v>596</v>
@@ -18861,7 +18861,7 @@
     </row>
     <row r="724" spans="1:5" ht="16.5">
       <c r="A724" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B724" s="3" t="s">
         <v>596</v>
@@ -18871,27 +18871,27 @@
         <v>67</v>
       </c>
       <c r="E724" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="725" spans="1:5" ht="16.5">
       <c r="A725" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B725" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C725" s="3"/>
       <c r="D725" t="s">
+        <v>855</v>
+      </c>
+      <c r="E725" t="s">
         <v>856</v>
-      </c>
-      <c r="E725" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="726" spans="1:5" ht="16.5">
       <c r="A726" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B726" s="3" t="s">
         <v>596</v>
@@ -18901,19 +18901,19 @@
         <v>268</v>
       </c>
       <c r="E726" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="727" spans="1:5" ht="16.5">
       <c r="A727" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B727" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C727" s="3"/>
       <c r="D727" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E727" t="s">
         <v>421</v>
@@ -18921,7 +18921,7 @@
     </row>
     <row r="728" spans="1:5" ht="16.5">
       <c r="A728" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B728" s="3" t="s">
         <v>596</v>
@@ -18936,7 +18936,7 @@
     </row>
     <row r="729" spans="1:5" ht="16.5">
       <c r="A729" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B729" s="3" t="s">
         <v>596</v>
@@ -18946,12 +18946,12 @@
         <v>214</v>
       </c>
       <c r="E729" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="730" spans="1:5" ht="16.5">
       <c r="A730" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B730" s="3" t="s">
         <v>596</v>
@@ -18961,12 +18961,12 @@
         <v>215</v>
       </c>
       <c r="E730" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="731" spans="1:5" ht="16.5">
       <c r="A731" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B731" s="3" t="s">
         <v>596</v>
@@ -18976,12 +18976,12 @@
         <v>499</v>
       </c>
       <c r="E731" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="732" spans="1:5" ht="16.5">
       <c r="A732" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B732" s="3" t="s">
         <v>596</v>
@@ -18996,7 +18996,7 @@
     </row>
     <row r="733" spans="1:5" ht="16.5">
       <c r="A733" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B733" s="3" t="s">
         <v>596</v>
@@ -19011,7 +19011,7 @@
     </row>
     <row r="734" spans="1:5" ht="16.5">
       <c r="A734" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B734" s="3" t="s">
         <v>596</v>
@@ -19026,7 +19026,7 @@
     </row>
     <row r="735" spans="1:5" ht="16.5">
       <c r="A735" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B735" s="3" t="s">
         <v>596</v>
@@ -19041,7 +19041,7 @@
     </row>
     <row r="736" spans="1:5" ht="16.5">
       <c r="A736" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B736" s="3" t="s">
         <v>596</v>
@@ -19056,14 +19056,14 @@
     </row>
     <row r="737" spans="1:5" ht="16.5">
       <c r="A737" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B737" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C737" s="3"/>
       <c r="D737" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E737" t="s">
         <v>504</v>
@@ -19071,7 +19071,7 @@
     </row>
     <row r="738" spans="1:5" ht="16.5">
       <c r="A738" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B738" s="3" t="s">
         <v>596</v>
@@ -19081,12 +19081,12 @@
         <v>406</v>
       </c>
       <c r="E738" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="739" spans="1:5" ht="16.5">
       <c r="A739" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B739" s="3" t="s">
         <v>596</v>
@@ -19101,7 +19101,7 @@
     </row>
     <row r="740" spans="1:5" ht="16.5">
       <c r="A740" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B740" s="3" t="s">
         <v>596</v>
@@ -19111,12 +19111,12 @@
         <v>531</v>
       </c>
       <c r="E740" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="741" spans="1:5" ht="16.5">
       <c r="A741" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B741" s="3" t="s">
         <v>596</v>
@@ -19126,12 +19126,12 @@
         <v>532</v>
       </c>
       <c r="E741" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="742" spans="1:5" ht="16.5">
       <c r="A742" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B742" s="3" t="s">
         <v>596</v>
@@ -19141,12 +19141,12 @@
         <v>534</v>
       </c>
       <c r="E742" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="743" spans="1:5" ht="16.5">
       <c r="A743" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B743" s="3" t="s">
         <v>596</v>
@@ -19156,12 +19156,12 @@
         <v>536</v>
       </c>
       <c r="E743" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="744" spans="1:5" ht="16.5">
       <c r="A744" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B744" s="3" t="s">
         <v>596</v>
@@ -19176,7 +19176,7 @@
     </row>
     <row r="745" spans="1:5" ht="16.5">
       <c r="A745" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B745" s="3" t="s">
         <v>596</v>
@@ -19186,27 +19186,27 @@
         <v>67</v>
       </c>
       <c r="E745" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="746" spans="1:5" ht="16.5">
       <c r="A746" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B746" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C746" s="3"/>
       <c r="D746" t="s">
+        <v>855</v>
+      </c>
+      <c r="E746" t="s">
         <v>856</v>
-      </c>
-      <c r="E746" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="747" spans="1:5" ht="16.5">
       <c r="A747" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B747" s="3" t="s">
         <v>596</v>
@@ -19216,19 +19216,19 @@
         <v>268</v>
       </c>
       <c r="E747" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="748" spans="1:5" ht="16.5">
       <c r="A748" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B748" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C748" s="3"/>
       <c r="D748" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E748" t="s">
         <v>421</v>
@@ -19236,7 +19236,7 @@
     </row>
     <row r="749" spans="1:5" ht="16.5">
       <c r="A749" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B749" s="3" t="s">
         <v>596</v>
@@ -19251,7 +19251,7 @@
     </row>
     <row r="750" spans="1:5" ht="16.5">
       <c r="A750" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B750" s="3" t="s">
         <v>596</v>
@@ -19261,12 +19261,12 @@
         <v>214</v>
       </c>
       <c r="E750" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="751" spans="1:5" ht="16.5">
       <c r="A751" s="25" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B751" s="3" t="s">
         <v>596</v>
@@ -19276,12 +19276,12 @@
         <v>215</v>
       </c>
       <c r="E751" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="752" spans="1:5" ht="16.5">
       <c r="A752" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B752" s="3" t="s">
         <v>596</v>
@@ -19296,7 +19296,7 @@
     </row>
     <row r="753" spans="1:5" ht="16.5">
       <c r="A753" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B753" s="3" t="s">
         <v>596</v>
@@ -19311,7 +19311,7 @@
     </row>
     <row r="754" spans="1:5" ht="16.5">
       <c r="A754" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B754" s="3" t="s">
         <v>596</v>
@@ -19326,7 +19326,7 @@
     </row>
     <row r="755" spans="1:5" ht="16.5">
       <c r="A755" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B755" s="3" t="s">
         <v>596</v>
@@ -19336,12 +19336,12 @@
         <v>527</v>
       </c>
       <c r="E755" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="756" spans="1:5" ht="16.5">
       <c r="A756" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B756" s="3" t="s">
         <v>596</v>
@@ -19351,19 +19351,19 @@
         <v>462</v>
       </c>
       <c r="E756" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="757" spans="1:5" ht="16.5">
       <c r="A757" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B757" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C757" s="3"/>
       <c r="D757" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E757" t="s">
         <v>431</v>
@@ -19371,22 +19371,22 @@
     </row>
     <row r="758" spans="1:5" ht="16.5">
       <c r="A758" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B758" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C758" s="3"/>
       <c r="D758" t="s">
+        <v>887</v>
+      </c>
+      <c r="E758" t="s">
         <v>888</v>
-      </c>
-      <c r="E758" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="759" spans="1:5" ht="16.5">
       <c r="A759" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B759" s="3" t="s">
         <v>596</v>
@@ -19401,7 +19401,7 @@
     </row>
     <row r="760" spans="1:5" ht="16.5">
       <c r="A760" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B760" s="3" t="s">
         <v>596</v>
@@ -19411,19 +19411,19 @@
         <v>531</v>
       </c>
       <c r="E760" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="761" spans="1:5" ht="16.5">
       <c r="A761" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B761" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C761" s="3"/>
       <c r="D761" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E761" t="s">
         <v>422</v>
@@ -19431,14 +19431,14 @@
     </row>
     <row r="762" spans="1:5" ht="16.5">
       <c r="A762" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B762" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C762" s="3"/>
       <c r="D762" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E762" t="s">
         <v>421</v>
@@ -19446,7 +19446,7 @@
     </row>
     <row r="763" spans="1:5" ht="16.5">
       <c r="A763" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B763" s="3" t="s">
         <v>596</v>
@@ -19456,12 +19456,12 @@
         <v>270</v>
       </c>
       <c r="E763" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="764" spans="1:5" ht="16.5">
       <c r="A764" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B764" s="3" t="s">
         <v>596</v>
@@ -19471,12 +19471,12 @@
         <v>214</v>
       </c>
       <c r="E764" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="765" spans="1:5" ht="16.5">
       <c r="A765" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B765" s="3" t="s">
         <v>596</v>
@@ -19486,12 +19486,12 @@
         <v>215</v>
       </c>
       <c r="E765" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="766" spans="1:5">
       <c r="A766" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B766" s="3" t="s">
         <v>596</v>
@@ -19506,14 +19506,14 @@
     </row>
     <row r="767" spans="1:5">
       <c r="A767" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B767" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C767" s="3"/>
       <c r="D767" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E767" t="s">
         <v>395</v>
@@ -19521,14 +19521,14 @@
     </row>
     <row r="768" spans="1:5">
       <c r="A768" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B768" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C768" s="3"/>
       <c r="D768" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E768" t="s">
         <v>389</v>
@@ -19536,7 +19536,7 @@
     </row>
     <row r="769" spans="1:5">
       <c r="A769" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B769" s="3" t="s">
         <v>596</v>
@@ -19551,7 +19551,7 @@
     </row>
     <row r="770" spans="1:5">
       <c r="A770" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B770" s="3" t="s">
         <v>596</v>
@@ -19566,7 +19566,7 @@
     </row>
     <row r="771" spans="1:5">
       <c r="A771" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B771" s="3" t="s">
         <v>596</v>
@@ -19581,7 +19581,7 @@
     </row>
     <row r="772" spans="1:5">
       <c r="A772" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B772" s="3" t="s">
         <v>596</v>
@@ -19596,14 +19596,14 @@
     </row>
     <row r="773" spans="1:5">
       <c r="A773" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B773" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C773" s="3"/>
       <c r="D773" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E773" t="s">
         <v>431</v>
@@ -19611,7 +19611,7 @@
     </row>
     <row r="774" spans="1:5">
       <c r="A774" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B774" s="3" t="s">
         <v>596</v>
@@ -19626,22 +19626,22 @@
     </row>
     <row r="775" spans="1:5">
       <c r="A775" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B775" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C775" s="3"/>
       <c r="D775" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E775" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="776" spans="1:5">
       <c r="A776" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B776" s="3" t="s">
         <v>596</v>
@@ -19656,7 +19656,7 @@
     </row>
     <row r="777" spans="1:5">
       <c r="A777" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B777" s="3" t="s">
         <v>596</v>
@@ -19666,12 +19666,12 @@
         <v>534</v>
       </c>
       <c r="E777" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="778" spans="1:5">
       <c r="A778" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B778" s="3" t="s">
         <v>596</v>
@@ -19681,12 +19681,12 @@
         <v>536</v>
       </c>
       <c r="E778" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="779" spans="1:5">
       <c r="A779" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B779" s="3" t="s">
         <v>596</v>
@@ -19696,12 +19696,12 @@
         <v>67</v>
       </c>
       <c r="E779" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="780" spans="1:5">
       <c r="A780" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B780" s="3" t="s">
         <v>596</v>
@@ -19711,12 +19711,12 @@
         <v>412</v>
       </c>
       <c r="E780" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="781" spans="1:5">
       <c r="A781" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B781" s="3" t="s">
         <v>596</v>
@@ -19731,7 +19731,7 @@
     </row>
     <row r="782" spans="1:5">
       <c r="A782" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B782" s="3" t="s">
         <v>596</v>
@@ -19746,7 +19746,7 @@
     </row>
     <row r="783" spans="1:5">
       <c r="A783" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B783" s="3" t="s">
         <v>596</v>
@@ -19756,12 +19756,12 @@
         <v>270</v>
       </c>
       <c r="E783" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="784" spans="1:5">
       <c r="A784" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B784" s="3" t="s">
         <v>596</v>
@@ -19771,12 +19771,12 @@
         <v>542</v>
       </c>
       <c r="E784" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="785" spans="1:5">
       <c r="A785" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B785" s="3" t="s">
         <v>596</v>
@@ -19786,12 +19786,12 @@
         <v>544</v>
       </c>
       <c r="E785" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="786" spans="1:5">
       <c r="A786" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B786" s="3" t="s">
         <v>596</v>
@@ -19801,12 +19801,12 @@
         <v>215</v>
       </c>
       <c r="E786" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="787" spans="1:5">
       <c r="A787" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B787" s="3" t="s">
         <v>596</v>
@@ -19816,19 +19816,19 @@
         <v>499</v>
       </c>
       <c r="E787" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="788" spans="1:5">
       <c r="A788" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B788" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C788" s="3"/>
       <c r="D788" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E788" t="s">
         <v>395</v>
@@ -19836,14 +19836,14 @@
     </row>
     <row r="789" spans="1:5">
       <c r="A789" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B789" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C789" s="3"/>
       <c r="D789" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E789" t="s">
         <v>389</v>
@@ -19851,7 +19851,7 @@
     </row>
     <row r="790" spans="1:5">
       <c r="A790" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B790" s="3" t="s">
         <v>596</v>
@@ -19866,7 +19866,7 @@
     </row>
     <row r="791" spans="1:5">
       <c r="A791" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B791" s="3" t="s">
         <v>596</v>
@@ -19881,7 +19881,7 @@
     </row>
     <row r="792" spans="1:5">
       <c r="A792" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B792" s="3" t="s">
         <v>596</v>
@@ -19896,7 +19896,7 @@
     </row>
     <row r="793" spans="1:5">
       <c r="A793" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B793" s="3" t="s">
         <v>596</v>
@@ -19911,14 +19911,14 @@
     </row>
     <row r="794" spans="1:5">
       <c r="A794" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B794" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C794" s="3"/>
       <c r="D794" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E794" t="s">
         <v>431</v>
@@ -19926,7 +19926,7 @@
     </row>
     <row r="795" spans="1:5">
       <c r="A795" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B795" s="3" t="s">
         <v>596</v>
@@ -19941,22 +19941,22 @@
     </row>
     <row r="796" spans="1:5">
       <c r="A796" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B796" s="3" t="s">
         <v>596</v>
       </c>
       <c r="C796" s="3"/>
       <c r="D796" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E796" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="797" spans="1:5">
       <c r="A797" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B797" s="3" t="s">
         <v>596</v>
@@ -19971,7 +19971,7 @@
     </row>
     <row r="798" spans="1:5">
       <c r="A798" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B798" s="3" t="s">
         <v>596</v>
@@ -19981,12 +19981,12 @@
         <v>534</v>
       </c>
       <c r="E798" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="799" spans="1:5">
       <c r="A799" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B799" s="3" t="s">
         <v>596</v>
@@ -19996,12 +19996,12 @@
         <v>536</v>
       </c>
       <c r="E799" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="800" spans="1:5">
       <c r="A800" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B800" s="3" t="s">
         <v>596</v>
@@ -20011,12 +20011,12 @@
         <v>67</v>
       </c>
       <c r="E800" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="801" spans="1:5">
       <c r="A801" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B801" s="3" t="s">
         <v>596</v>
@@ -20031,7 +20031,7 @@
     </row>
     <row r="802" spans="1:5">
       <c r="A802" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B802" s="3" t="s">
         <v>596</v>
@@ -20046,7 +20046,7 @@
     </row>
     <row r="803" spans="1:5">
       <c r="A803" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B803" s="3" t="s">
         <v>596</v>
@@ -20061,7 +20061,7 @@
     </row>
     <row r="804" spans="1:5">
       <c r="A804" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B804" s="3" t="s">
         <v>596</v>
@@ -20076,7 +20076,7 @@
     </row>
     <row r="805" spans="1:5">
       <c r="A805" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B805" s="3" t="s">
         <v>596</v>
@@ -20086,12 +20086,12 @@
         <v>270</v>
       </c>
       <c r="E805" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="806" spans="1:5">
       <c r="A806" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B806" s="3" t="s">
         <v>596</v>
@@ -20101,12 +20101,12 @@
         <v>542</v>
       </c>
       <c r="E806" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="807" spans="1:5">
       <c r="A807" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B807" s="3" t="s">
         <v>596</v>
@@ -20116,12 +20116,12 @@
         <v>544</v>
       </c>
       <c r="E807" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="808" spans="1:5">
       <c r="A808" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B808" s="3" t="s">
         <v>596</v>
@@ -20131,7 +20131,7 @@
         <v>215</v>
       </c>
       <c r="E808" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="809" spans="1:5">
@@ -21630,6 +21630,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1b00f46c-3b5f-4331-86e9-781a15a27617" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001C9F242BA08D5448BD54F44CFC5724EE" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1da9a53cfbc9630190da298061f0a1b8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8d9926d0-0824-429b-9ce7-e0a3e3153b89" xmlns:ns4="1b00f46c-3b5f-4331-86e9-781a15a27617" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c363a18788a1ee53fffc53639eb0186b" ns3:_="" ns4:_="">
     <xsd:import namespace="8d9926d0-0824-429b-9ce7-e0a3e3153b89"/>
@@ -21856,14 +21864,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1b00f46c-3b5f-4331-86e9-781a15a27617" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C53BC2E-8A9E-4A85-93E8-958094667844}">
   <ds:schemaRefs>
@@ -21873,6 +21873,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8B90F5-EBD9-46C8-A4AD-41D7B713BE29}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="1b00f46c-3b5f-4331-86e9-781a15a27617"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8d9926d0-0824-429b-9ce7-e0a3e3153b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83FC1C06-2FE4-4B02-A515-84560BE21A99}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21889,21 +21906,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8B90F5-EBD9-46C8-A4AD-41D7B713BE29}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="1b00f46c-3b5f-4331-86e9-781a15a27617"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8d9926d0-0824-429b-9ce7-e0a3e3153b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/import/products.xlsx
+++ b/import/products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive - University of East Anglia\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03FC50AD-3A34-457D-991C-BEF7E89E3A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D03B29-A337-494B-8390-15BE43445693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
+    <workbookView xWindow="7200" yWindow="1140" windowWidth="21600" windowHeight="11295" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="Specifications" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -119,12 +118,6 @@
     <t>Main-Category</t>
   </si>
   <si>
-    <t>Interactive Flat Panel</t>
-  </si>
-  <si>
-    <t>itcHUB</t>
-  </si>
-  <si>
     <t>TV-S8198</t>
   </si>
   <si>
@@ -1089,6 +1082,12 @@
   </si>
   <si>
     <t>The camera module has a knob lens privacy cover, and users can turn off the lens when the camera is not in use to ensure privacy and security.</t>
+  </si>
+  <si>
+    <t>interactive-flat-panel</t>
+  </si>
+  <si>
+    <t>itchub</t>
   </si>
 </sst>
 </file>
@@ -1148,7 +1147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1166,16 +1165,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1207,16 +1215,6 @@
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1231,7 +1229,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{485EF06A-B474-447D-A8F9-89BDB6093278}" name="Table1" displayName="Table1" ref="A1:H47" totalsRowShown="0" headerRowDxfId="4" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{485EF06A-B474-447D-A8F9-89BDB6093278}" name="Table1" displayName="Table1" ref="A1:H47" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:H47" xr:uid="{485EF06A-B474-447D-A8F9-89BDB6093278}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8B000398-16FD-4922-ADD1-EEFE78CEDB7B}" name="Name"/>
@@ -1248,10 +1246,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2FA1D685-D8D8-4A34-AB8D-1A46F55D4A8E}" name="Table2" displayName="Table2" ref="A1:B124" totalsRowShown="0" headerRowDxfId="2" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2FA1D685-D8D8-4A34-AB8D-1A46F55D4A8E}" name="Table2" displayName="Table2" ref="A1:B124" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="A1:B124" xr:uid="{2FA1D685-D8D8-4A34-AB8D-1A46F55D4A8E}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B6913FB2-003F-4F8F-88B4-A069ABD8343E}" name="ProductName" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{B6913FB2-003F-4F8F-88B4-A069ABD8343E}" name="ProductName" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{4F86F527-609B-41A7-8685-657266DE69B4}" name="Bullets" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1616,54 +1614,54 @@
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>347</v>
       </c>
       <c r="D2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>347</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>348</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1864,986 +1862,986 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
         <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="B53" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>50</v>
+        <v>25</v>
+      </c>
+      <c r="B54" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>47</v>
+        <v>25</v>
+      </c>
+      <c r="B55" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>46</v>
+        <v>25</v>
+      </c>
+      <c r="B56" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>45</v>
+        <v>25</v>
+      </c>
+      <c r="B57" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>40</v>
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>39</v>
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>41</v>
+        <v>25</v>
+      </c>
+      <c r="B60" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>43</v>
+        <v>25</v>
+      </c>
+      <c r="B62" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>44</v>
+        <v>25</v>
+      </c>
+      <c r="B63" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>42</v>
+        <v>25</v>
+      </c>
+      <c r="B64" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>38</v>
+        <v>25</v>
+      </c>
+      <c r="B65" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>37</v>
+        <v>25</v>
+      </c>
+      <c r="B66" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>36</v>
+        <v>25</v>
+      </c>
+      <c r="B67" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>35</v>
+        <v>25</v>
+      </c>
+      <c r="B68" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="B69" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="B70" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>32</v>
+        <v>25</v>
+      </c>
+      <c r="B71" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B72" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B73" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B74" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B75" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B76" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B77" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B78" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B79" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B80" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B81" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B82" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B84" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B85" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B86" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B87" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B88" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B89" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B91" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B93" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B95" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B100" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B102" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B103" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B104" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B105" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B106" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B107" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B108" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B109" s="9" t="s">
-        <v>297</v>
+        <v>97</v>
+      </c>
+      <c r="B109" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B110" s="9" t="s">
-        <v>312</v>
+        <v>97</v>
+      </c>
+      <c r="B110" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B111" s="9" t="s">
-        <v>311</v>
+        <v>97</v>
+      </c>
+      <c r="B111" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B112" s="9" t="s">
-        <v>310</v>
+        <v>97</v>
+      </c>
+      <c r="B112" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>309</v>
+        <v>97</v>
+      </c>
+      <c r="B113" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B114" s="9" t="s">
-        <v>298</v>
+        <v>97</v>
+      </c>
+      <c r="B114" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>308</v>
+        <v>97</v>
+      </c>
+      <c r="B115" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B116" s="9" t="s">
-        <v>307</v>
+        <v>97</v>
+      </c>
+      <c r="B116" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B117" s="9" t="s">
-        <v>306</v>
+        <v>97</v>
+      </c>
+      <c r="B117" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B118" s="9" t="s">
-        <v>305</v>
+        <v>97</v>
+      </c>
+      <c r="B118" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B119" s="9" t="s">
-        <v>304</v>
+        <v>97</v>
+      </c>
+      <c r="B119" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B120" s="9" t="s">
-        <v>303</v>
+        <v>97</v>
+      </c>
+      <c r="B120" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B121" s="9" t="s">
-        <v>302</v>
+        <v>97</v>
+      </c>
+      <c r="B121" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B122" s="9" t="s">
-        <v>300</v>
+        <v>97</v>
+      </c>
+      <c r="B122" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B123" s="9" t="s">
-        <v>301</v>
+        <v>97</v>
+      </c>
+      <c r="B123" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B124" s="9" t="s">
-        <v>299</v>
+        <v>97</v>
+      </c>
+      <c r="B124" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -2868,51 +2866,51 @@
     <col min="5" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>27</v>
+      <c r="A2" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>27</v>
+      <c r="A4" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>20</v>
@@ -2921,68 +2919,68 @@
         <v>14</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="5" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="5" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>27</v>
+      <c r="A9" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
@@ -2991,460 +2989,460 @@
         <v>21</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="D10" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="D11" s="5">
         <v>0.85</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>27</v>
+      <c r="A12" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="4" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="4" t="s">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="4" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="4" t="s">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="4" t="s">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="4" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="4" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="4" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="4" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D23" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="D24" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="4" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="4" t="s">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="4" t="s">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="4" t="s">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D28" s="4" t="s">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="4" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" s="4" t="s">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="4" t="s">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D33" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="4" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D34" s="4" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="4" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="4" t="s">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="4" t="s">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D37" s="4" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="4" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D38" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="4" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D39" s="4" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="4" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" s="4" t="s">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D41" s="4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
-        <v>27</v>
+      <c r="A42" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>20</v>
@@ -3453,26 +3451,26 @@
         <v>15</v>
       </c>
       <c r="D42" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>183</v>
-      </c>
       <c r="D43" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
-        <v>27</v>
+      <c r="A44" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>20</v>
@@ -3481,40 +3479,40 @@
         <v>17</v>
       </c>
       <c r="D44" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="4" t="s">
+      <c r="D45" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D46" s="4" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
-        <v>27</v>
+      <c r="A47" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>20</v>
@@ -3523,26 +3521,26 @@
         <v>22</v>
       </c>
       <c r="D47" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>191</v>
-      </c>
       <c r="D48" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
-        <v>27</v>
+      <c r="A49" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>20</v>
@@ -3551,12 +3549,12 @@
         <v>18</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
-        <v>27</v>
+      <c r="A50" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>20</v>
@@ -3565,110 +3563,110 @@
         <v>19</v>
       </c>
       <c r="D50" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C51" s="4" t="s">
+      <c r="D51" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="D51" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" s="4" t="s">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D53" s="4" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C53" s="4" t="s">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" s="4" t="s">
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D55" s="4" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C55" s="4" t="s">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>205</v>
-      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
-        <v>27</v>
+      <c r="A58" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>20</v>
@@ -3677,110 +3675,110 @@
         <v>16</v>
       </c>
       <c r="D58" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" s="4" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60" s="4" t="s">
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D61" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C61" s="4" t="s">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>20</v>
@@ -3789,68 +3787,68 @@
         <v>14</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>20</v>
@@ -3859,32 +3857,32 @@
         <v>21</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D73" s="3">
         <v>0.85</v>
@@ -3892,91 +3890,91 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>20</v>
@@ -3985,502 +3983,502 @@
         <v>13</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>20</v>
@@ -4489,26 +4487,26 @@
         <v>15</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>20</v>
@@ -4517,40 +4515,40 @@
         <v>17</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>20</v>
@@ -4559,26 +4557,26 @@
         <v>22</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>20</v>
@@ -4587,12 +4585,12 @@
         <v>18</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>20</v>
@@ -4601,110 +4599,110 @@
         <v>19</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>20</v>
@@ -4713,63 +4711,63 @@
         <v>16</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -5917,20 +5915,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1b00f46c-3b5f-4331-86e9-781a15a27617" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1b00f46c-3b5f-4331-86e9-781a15a27617" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5953,6 +5951,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C53BC2E-8A9E-4A85-93E8-958094667844}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8B90F5-EBD9-46C8-A4AD-41D7B713BE29}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -5967,12 +5973,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C53BC2E-8A9E-4A85-93E8-958094667844}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>